--- a/Faculties/Law/Undergrad Modules Law.xlsx
+++ b/Faculties/Law/Undergrad Modules Law.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Law/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DC2B96B-CA48-4E65-BCEF-DAD281625A95}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13370260-080D-405B-B60B-78EA7FC559F4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="708" yWindow="936" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -108,15 +108,9 @@
     <t>BCom Law</t>
   </si>
   <si>
-    <t>ALB131 (for 4-yr students)</t>
-  </si>
-  <si>
     <t>BSL100</t>
   </si>
   <si>
-    <t>Basic Skills for Law 100 (ECP)</t>
-  </si>
-  <si>
     <t>LLB-ECP</t>
   </si>
   <si>
@@ -456,9 +450,6 @@
     <t>FAM100</t>
   </si>
   <si>
-    <t>Family Law 100 (ECP)</t>
-  </si>
-  <si>
     <t>FAM121</t>
   </si>
   <si>
@@ -585,9 +576,6 @@
     <t>ILL100</t>
   </si>
   <si>
-    <t>Introduction to Law 100 (ECP)</t>
-  </si>
-  <si>
     <t>ILL111</t>
   </si>
   <si>
@@ -603,9 +591,6 @@
     <t>ILL200</t>
   </si>
   <si>
-    <t>Introduction to Law 200 (ECP)</t>
-  </si>
-  <si>
     <t>INS311</t>
   </si>
   <si>
@@ -732,9 +717,6 @@
     <t>LOP100</t>
   </si>
   <si>
-    <t>Law of Persons 100 (ECP)</t>
-  </si>
-  <si>
     <t>LOP112</t>
   </si>
   <si>
@@ -759,9 +741,6 @@
     <t>Principles of Business Management 131/132</t>
   </si>
   <si>
-    <t>IEB131 (for Non-EMS)</t>
-  </si>
-  <si>
     <t>MAN201</t>
   </si>
   <si>
@@ -1152,9 +1131,6 @@
     <t>Administrative Law 113</t>
   </si>
   <si>
-    <t>HCert (Forensic Examination)</t>
-  </si>
-  <si>
     <t>CRI112</t>
   </si>
   <si>
@@ -1191,9 +1167,6 @@
     <t>Introduction to Law 611</t>
   </si>
   <si>
-    <t>AdvDip (Labour Law)</t>
-  </si>
-  <si>
     <t>LAB612</t>
   </si>
   <si>
@@ -1234,6 +1207,33 @@
   </si>
   <si>
     <t>Labour and Social Security Law 618</t>
+  </si>
+  <si>
+    <t>ALB131 for 4-yr students</t>
+  </si>
+  <si>
+    <t>Basic Skills for Law 100 ECP</t>
+  </si>
+  <si>
+    <t>Family Law 100 ECP</t>
+  </si>
+  <si>
+    <t>Introduction to Law 100 ECP</t>
+  </si>
+  <si>
+    <t>Introduction to Law 200 ECP</t>
+  </si>
+  <si>
+    <t>Law of Persons 100 ECP</t>
+  </si>
+  <si>
+    <t>IEB131 for Non-EMS</t>
+  </si>
+  <si>
+    <t>HCert Forensic Examination</t>
+  </si>
+  <si>
+    <t>AdvDip Labour Law</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1724,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>394</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -1732,16 +1732,16 @@
     </row>
     <row r="8" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>395</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>18</v>
@@ -1752,16 +1752,16 @@
     </row>
     <row r="9" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>18</v>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -1784,7 +1784,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>18</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>17</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
@@ -1864,7 +1864,7 @@
         <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>18</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
@@ -1884,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>18</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="16" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
@@ -1912,16 +1912,16 @@
     </row>
     <row r="17" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>18</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>8</v>
@@ -1944,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>18</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>8</v>
@@ -1964,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>18</v>
@@ -1972,16 +1972,16 @@
     </row>
     <row r="20" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>18</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>8</v>
@@ -2004,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>18</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1">
         <v>3</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>8</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="24" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>8</v>
@@ -2064,18 +2064,18 @@
         <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>8</v>
@@ -2084,7 +2084,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>18</v>
@@ -2092,16 +2092,16 @@
     </row>
     <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>18</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="27" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>8</v>
@@ -2124,7 +2124,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>18</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="28" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>8</v>
@@ -2144,7 +2144,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>18</v>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>17</v>
@@ -2172,16 +2172,16 @@
     </row>
     <row r="30" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>18</v>
@@ -2192,19 +2192,19 @@
     </row>
     <row r="31" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>18</v>
@@ -2212,39 +2212,39 @@
     </row>
     <row r="32" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>18</v>
@@ -2252,19 +2252,19 @@
     </row>
     <row r="34" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>18</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="35" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C35" s="1">
         <v>2</v>
@@ -2284,7 +2284,7 @@
         <v>26</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>18</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="36" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
@@ -2304,18 +2304,18 @@
         <v>26</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C37" s="1">
         <v>3</v>
@@ -2324,7 +2324,7 @@
         <v>26</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>18</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="38" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C38" s="1">
         <v>3</v>
@@ -2344,7 +2344,7 @@
         <v>26</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>18</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C39" s="1">
         <v>3</v>
@@ -2364,7 +2364,7 @@
         <v>26</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>18</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="40" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C40" s="1">
         <v>3</v>
@@ -2384,7 +2384,7 @@
         <v>26</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>18</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="41" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C41" s="1">
         <v>3</v>
@@ -2404,7 +2404,7 @@
         <v>26</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>18</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="42" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C42" s="1">
         <v>3</v>
@@ -2424,7 +2424,7 @@
         <v>26</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>18</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="43" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>9</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="44" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>8</v>
@@ -2472,16 +2472,16 @@
     </row>
     <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C45" s="1">
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>18</v>
@@ -2492,19 +2492,19 @@
     </row>
     <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>18</v>
@@ -2512,19 +2512,19 @@
     </row>
     <row r="47" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C47" s="1">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>18</v>
@@ -2532,16 +2532,16 @@
     </row>
     <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>18</v>
@@ -2552,19 +2552,19 @@
     </row>
     <row r="49" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C49" s="1">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>18</v>
@@ -2572,16 +2572,16 @@
     </row>
     <row r="50" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C50" s="1">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>18</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="51" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>8</v>
@@ -2612,13 +2612,13 @@
     </row>
     <row r="52" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>9</v>
@@ -2632,13 +2632,13 @@
     </row>
     <row r="53" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>9</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>8</v>
@@ -2675,7 +2675,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>8</v>
@@ -2684,7 +2684,7 @@
         <v>9</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>18</v>
@@ -2692,16 +2692,16 @@
     </row>
     <row r="56" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>143</v>
+        <v>396</v>
       </c>
       <c r="C56" s="1">
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>18</v>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="57" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>18</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="58" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>8</v>
@@ -2744,7 +2744,7 @@
         <v>9</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>18</v>
@@ -2752,16 +2752,16 @@
     </row>
     <row r="59" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>18</v>
@@ -2772,19 +2772,19 @@
     </row>
     <row r="60" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C60" s="1">
         <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>18</v>
@@ -2792,19 +2792,19 @@
     </row>
     <row r="61" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C61" s="1">
         <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>18</v>
@@ -2812,19 +2812,19 @@
     </row>
     <row r="62" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C62" s="1">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>18</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="63" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C63" s="1">
         <v>1</v>
@@ -2847,15 +2847,15 @@
         <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
@@ -2864,7 +2864,7 @@
         <v>26</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>18</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="65" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C65" s="1">
         <v>2</v>
@@ -2884,7 +2884,7 @@
         <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>18</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="66" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C66" s="1">
         <v>3</v>
@@ -2904,18 +2904,18 @@
         <v>26</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C67" s="1">
         <v>3</v>
@@ -2924,7 +2924,7 @@
         <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>18</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="68" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C68" s="1">
         <v>3</v>
@@ -2944,7 +2944,7 @@
         <v>26</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>18</v>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C69" s="1">
         <v>3</v>
@@ -2964,7 +2964,7 @@
         <v>26</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>18</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="70" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>8</v>
@@ -2984,7 +2984,7 @@
         <v>9</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>18</v>
@@ -2992,16 +2992,16 @@
     </row>
     <row r="71" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>18</v>
@@ -3012,16 +3012,16 @@
     </row>
     <row r="72" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>18</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="73" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>8</v>
@@ -3044,7 +3044,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>18</v>
@@ -3052,13 +3052,13 @@
     </row>
     <row r="74" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>9</v>
@@ -3072,16 +3072,16 @@
     </row>
     <row r="75" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>186</v>
+        <v>397</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>18</v>
@@ -3092,16 +3092,16 @@
     </row>
     <row r="76" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>18</v>
@@ -3112,16 +3112,16 @@
     </row>
     <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>18</v>
@@ -3132,16 +3132,16 @@
     </row>
     <row r="78" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>192</v>
+        <v>398</v>
       </c>
       <c r="C78" s="1">
         <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>18</v>
@@ -3152,30 +3152,30 @@
     </row>
     <row r="79" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>8</v>
@@ -3184,7 +3184,7 @@
         <v>9</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>18</v>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="81" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>8</v>
@@ -3204,7 +3204,7 @@
         <v>9</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>18</v>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="82" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C82" s="1">
         <v>1</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C83" s="1">
         <v>2</v>
@@ -3244,7 +3244,7 @@
         <v>26</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>18</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="84" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C84" s="1">
         <v>2</v>
@@ -3264,7 +3264,7 @@
         <v>26</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>18</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="85" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C85" s="1">
         <v>2</v>
@@ -3284,7 +3284,7 @@
         <v>26</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>18</v>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="86" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
@@ -3304,7 +3304,7 @@
         <v>26</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>18</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C87" s="1">
         <v>3</v>
@@ -3324,7 +3324,7 @@
         <v>26</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>18</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C88" s="1">
         <v>3</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="89" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C89" s="1">
         <v>3</v>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="90" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C90" s="1">
         <v>3</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="91" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>17</v>
@@ -3415,13 +3415,13 @@
         <v>23</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>18</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="93" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>8</v>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="94" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>8</v>
@@ -3472,13 +3472,13 @@
     </row>
     <row r="95" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>9</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="96" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>8</v>
@@ -3512,10 +3512,10 @@
     </row>
     <row r="97" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>8</v>
@@ -3524,7 +3524,7 @@
         <v>9</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>18</v>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="98" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>8</v>
@@ -3544,7 +3544,7 @@
         <v>9</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>18</v>
@@ -3552,16 +3552,16 @@
     </row>
     <row r="99" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>235</v>
+        <v>399</v>
       </c>
       <c r="C99" s="1">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>18</v>
@@ -3572,16 +3572,16 @@
     </row>
     <row r="100" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>18</v>
@@ -3592,10 +3592,10 @@
     </row>
     <row r="101" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>8</v>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="102" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>8</v>
@@ -3624,7 +3624,7 @@
         <v>9</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>18</v>
@@ -3632,19 +3632,19 @@
     </row>
     <row r="103" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>244</v>
+        <v>400</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>18</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C104" s="1">
         <v>2</v>
@@ -3667,15 +3667,15 @@
         <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
@@ -3684,18 +3684,18 @@
         <v>26</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -3704,7 +3704,7 @@
         <v>26</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>18</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>
@@ -3724,7 +3724,7 @@
         <v>26</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>18</v>
@@ -3732,10 +3732,10 @@
     </row>
     <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C108" s="1">
         <v>3</v>
@@ -3744,7 +3744,7 @@
         <v>26</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>18</v>
@@ -3752,10 +3752,10 @@
     </row>
     <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C109" s="1">
         <v>3</v>
@@ -3764,18 +3764,18 @@
         <v>26</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C110" s="1">
         <v>3</v>
@@ -3784,18 +3784,18 @@
         <v>26</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C111" s="1">
         <v>3</v>
@@ -3804,7 +3804,7 @@
         <v>26</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>18</v>
@@ -3812,16 +3812,16 @@
     </row>
     <row r="112" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
@@ -3832,16 +3832,16 @@
     </row>
     <row r="113" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>18</v>
@@ -3852,19 +3852,19 @@
     </row>
     <row r="114" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C114" s="1">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>18</v>
@@ -3872,16 +3872,16 @@
     </row>
     <row r="115" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C115" s="1">
         <v>2</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>18</v>
@@ -3892,16 +3892,16 @@
     </row>
     <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C116" s="1">
         <v>2</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>18</v>
@@ -3912,16 +3912,16 @@
     </row>
     <row r="117" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C117" s="1">
         <v>2</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>18</v>
@@ -3932,19 +3932,19 @@
     </row>
     <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C118" s="1">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>18</v>
@@ -3952,16 +3952,16 @@
     </row>
     <row r="119" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C119" s="1">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>18</v>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C120" s="1">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>18</v>
@@ -3992,16 +3992,16 @@
     </row>
     <row r="121" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C121" s="1">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>18</v>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="122" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>8</v>
@@ -4032,16 +4032,16 @@
     </row>
     <row r="123" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>18</v>
@@ -4052,16 +4052,16 @@
     </row>
     <row r="124" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>18</v>
@@ -4072,19 +4072,19 @@
     </row>
     <row r="125" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C125" s="1">
         <v>2</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>18</v>
@@ -4092,16 +4092,16 @@
     </row>
     <row r="126" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C126" s="1">
         <v>2</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>18</v>
@@ -4112,19 +4112,19 @@
     </row>
     <row r="127" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C127" s="1">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>18</v>
@@ -4132,16 +4132,16 @@
     </row>
     <row r="128" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C128" s="1">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>18</v>
@@ -4152,16 +4152,16 @@
     </row>
     <row r="129" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>18</v>
@@ -4172,16 +4172,16 @@
     </row>
     <row r="130" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>18</v>
@@ -4192,16 +4192,16 @@
     </row>
     <row r="131" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>18</v>
@@ -4212,16 +4212,16 @@
     </row>
     <row r="132" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>18</v>
@@ -4232,16 +4232,16 @@
     </row>
     <row r="133" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C133" s="1">
         <v>2</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>18</v>
@@ -4252,16 +4252,16 @@
     </row>
     <row r="134" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C134" s="1">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>18</v>
@@ -4272,16 +4272,16 @@
     </row>
     <row r="135" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C135" s="1">
         <v>2</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>18</v>
@@ -4292,16 +4292,16 @@
     </row>
     <row r="136" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>18</v>
@@ -4312,19 +4312,19 @@
     </row>
     <row r="137" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C137" s="1">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>18</v>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="138" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C138" s="1">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>18</v>
@@ -4352,16 +4352,16 @@
     </row>
     <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C139" s="1">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>18</v>
@@ -4372,16 +4372,16 @@
     </row>
     <row r="140" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C140" s="1">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>18</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="141" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>17</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="142" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C142" s="1">
         <v>1</v>
@@ -4427,15 +4427,15 @@
         <v>18</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>8</v>
@@ -4447,15 +4447,15 @@
         <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>17</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="145" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>8</v>
@@ -4484,7 +4484,7 @@
         <v>9</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>18</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="146" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>8</v>
@@ -4504,7 +4504,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>18</v>
@@ -4512,16 +4512,16 @@
     </row>
     <row r="147" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C147" s="1">
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>18</v>
@@ -4532,16 +4532,16 @@
     </row>
     <row r="148" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C148" s="1">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>18</v>
@@ -4552,36 +4552,36 @@
     </row>
     <row r="149" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>18</v>
@@ -4592,39 +4592,39 @@
     </row>
     <row r="151" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C151" s="1">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C152" s="1">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>18</v>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="153" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>8</v>
@@ -4652,16 +4652,16 @@
     </row>
     <row r="154" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>18</v>
@@ -4672,13 +4672,13 @@
     </row>
     <row r="155" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>9</v>
@@ -4692,16 +4692,16 @@
     </row>
     <row r="156" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D156" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>18</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="157" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>8</v>
@@ -4724,7 +4724,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>18</v>
@@ -4732,10 +4732,10 @@
     </row>
     <row r="158" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>8</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="159" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>8</v>
@@ -4764,7 +4764,7 @@
         <v>9</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>18</v>
@@ -4772,13 +4772,13 @@
     </row>
     <row r="160" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>9</v>
@@ -4792,19 +4792,19 @@
     </row>
     <row r="161" spans="1:6" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>18</v>
@@ -4812,16 +4812,16 @@
     </row>
     <row r="162" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C162" s="1">
         <v>1</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>18</v>
@@ -4832,16 +4832,16 @@
     </row>
     <row r="163" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C163" s="1">
         <v>1</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>18</v>
@@ -4852,16 +4852,16 @@
     </row>
     <row r="164" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C164" s="1">
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>18</v>
@@ -4872,16 +4872,16 @@
     </row>
     <row r="165" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C165" s="1">
         <v>1</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>18</v>
@@ -4892,16 +4892,16 @@
     </row>
     <row r="166" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C166" s="1">
         <v>1</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>18</v>
@@ -4912,16 +4912,16 @@
     </row>
     <row r="167" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C167" s="1">
         <v>1</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>18</v>
@@ -4952,16 +4952,16 @@
     </row>
     <row r="169" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C169" s="1">
         <v>1</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>18</v>
@@ -4972,16 +4972,16 @@
     </row>
     <row r="170" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C170" s="1">
         <v>1</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>18</v>
@@ -4992,16 +4992,16 @@
     </row>
     <row r="171" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C171" s="1">
         <v>1</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>18</v>
@@ -5012,16 +5012,16 @@
     </row>
     <row r="172" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C172" s="1">
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>18</v>
@@ -5032,16 +5032,16 @@
     </row>
     <row r="173" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C173" s="1">
         <v>1</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>18</v>
@@ -5052,16 +5052,16 @@
     </row>
     <row r="174" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C174" s="1">
         <v>1</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>18</v>
@@ -5072,16 +5072,16 @@
     </row>
     <row r="175" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C175" s="1">
         <v>1</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>18</v>
@@ -5092,16 +5092,16 @@
     </row>
     <row r="176" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C176" s="1">
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>18</v>

--- a/Faculties/Law/Undergrad Modules Law.xlsx
+++ b/Faculties/Law/Undergrad Modules Law.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Law/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Law\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13370260-080D-405B-B60B-78EA7FC559F4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BD7586-DD65-4623-BCEB-04B3589DD406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="708" yWindow="936" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="403">
   <si>
     <t>Module Code</t>
   </si>
@@ -54,9 +54,6 @@
     <t>4 or 5</t>
   </si>
   <si>
-    <t>LLB, LLB-ECP</t>
-  </si>
-  <si>
     <t>CIV302 &amp; CON202</t>
   </si>
   <si>
@@ -105,15 +102,9 @@
     <t>Academic Literacy for Commerce 131/132</t>
   </si>
   <si>
-    <t>BCom Law</t>
-  </si>
-  <si>
     <t>BSL100</t>
   </si>
   <si>
-    <t>LLB-ECP</t>
-  </si>
-  <si>
     <t>BSL101</t>
   </si>
   <si>
@@ -123,9 +114,6 @@
     <t>1 or 2</t>
   </si>
   <si>
-    <t>LLB, BA Law, BCom Law</t>
-  </si>
-  <si>
     <t>BUS132</t>
   </si>
   <si>
@@ -180,9 +168,6 @@
     <t>Law of Contract 301</t>
   </si>
   <si>
-    <t>LLB, LLB-ECP, BA Law, BCom Law</t>
-  </si>
-  <si>
     <t>CNT431</t>
   </si>
   <si>
@@ -249,9 +234,6 @@
     <t>Criminal Law 202</t>
   </si>
   <si>
-    <t>LLB, LLB-ECP, BA Law</t>
-  </si>
-  <si>
     <t>CRL431</t>
   </si>
   <si>
@@ -282,9 +264,6 @@
     <t>Introduction to Microeconomics 151</t>
   </si>
   <si>
-    <t>BCom Law, LLB</t>
-  </si>
-  <si>
     <t>QSC131/132</t>
   </si>
   <si>
@@ -378,9 +357,6 @@
     <t>English 111</t>
   </si>
   <si>
-    <t>BA Law</t>
-  </si>
-  <si>
     <t>ENG121</t>
   </si>
   <si>
@@ -597,9 +573,6 @@
     <t>Law of Insolvency 311</t>
   </si>
   <si>
-    <t>LLB, LLB-ECP, BCom Law</t>
-  </si>
-  <si>
     <t>INT431</t>
   </si>
   <si>
@@ -1230,10 +1203,37 @@
     <t>IEB131 for Non-EMS</t>
   </si>
   <si>
-    <t>HCert Forensic Examination</t>
-  </si>
-  <si>
-    <t>AdvDip Labour Law</t>
+    <t>LLB 7162, LLB-ECP 7172</t>
+  </si>
+  <si>
+    <t>LLB-ECP 7172</t>
+  </si>
+  <si>
+    <t>BCom Law 7211</t>
+  </si>
+  <si>
+    <t>BCom Law 7211, LLB</t>
+  </si>
+  <si>
+    <t>LLB 7162, LLB-ECP 7172, BCom Law 7211</t>
+  </si>
+  <si>
+    <t>LLB 7162, BA Law 7221, BCom Law 7211</t>
+  </si>
+  <si>
+    <t>LLB 7162, LLB-ECP 7172, BA Law 7221, BCom Law 7211</t>
+  </si>
+  <si>
+    <t>LLB 7162, LLB-ECP 7172, BA Law 7221</t>
+  </si>
+  <si>
+    <t>BA Law 7221</t>
+  </si>
+  <si>
+    <t>HCert Forensic Examination 7115</t>
+  </si>
+  <si>
+    <t>AdvDip Labour Law 7311</t>
   </si>
 </sst>
 </file>
@@ -1315,10 +1315,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1584,9 +1580,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
     <col min="6" max="6" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1621,3201 +1618,3201 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>397</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>51</v>
+        <v>398</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>51</v>
+        <v>398</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>51</v>
+        <v>398</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C35" s="1">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C37" s="1">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C39" s="1">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C40" s="1">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C41" s="1">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C42" s="1">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C45" s="1">
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1">
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C49" s="1">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C50" s="1">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C56" s="1">
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>32</v>
+        <v>397</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C60" s="1">
         <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C61" s="1">
         <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C62" s="1">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C63" s="1">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C64" s="1">
         <v>2</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C65" s="1">
         <v>2</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C66" s="1">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C67" s="1">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C68" s="1">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C69" s="1">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>32</v>
+        <v>397</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>32</v>
+        <v>397</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C78" s="1">
         <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>190</v>
+        <v>396</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C82" s="1">
         <v>1</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C83" s="1">
         <v>2</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C84" s="1">
         <v>2</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C85" s="1">
         <v>2</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C87" s="1">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C88" s="1">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C89" s="1">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C90" s="1">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>51</v>
+        <v>398</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C99" s="1">
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>32</v>
+        <v>397</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>190</v>
+        <v>396</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C104" s="1">
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C108" s="1">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C109" s="1">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C110" s="1">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C111" s="1">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C112" s="1">
         <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C114" s="1">
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C115" s="1">
         <v>2</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1">
         <v>2</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C117" s="1">
         <v>2</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C119" s="1">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C120" s="1">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C121" s="1">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C125" s="1">
         <v>2</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C126" s="1">
         <v>2</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C128" s="1">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C133" s="1">
         <v>2</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C134" s="1">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C135" s="1">
         <v>2</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C137" s="1">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C138" s="1">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C139" s="1">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C140" s="1">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C142" s="1">
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>26</v>
+        <v>394</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C147" s="1">
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C148" s="1">
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C151" s="1">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C152" s="1">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>117</v>
+        <v>400</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>51</v>
+        <v>398</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>51</v>
+        <v>398</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>9</v>
+        <v>392</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C162" s="1">
         <v>1</v>
@@ -4824,18 +4821,18 @@
         <v>401</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C163" s="1">
         <v>1</v>
@@ -4844,18 +4841,18 @@
         <v>401</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C164" s="1">
         <v>1</v>
@@ -4864,18 +4861,18 @@
         <v>401</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C165" s="1">
         <v>1</v>
@@ -4884,18 +4881,18 @@
         <v>401</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C166" s="1">
         <v>1</v>
@@ -4904,18 +4901,18 @@
         <v>401</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C167" s="1">
         <v>1</v>
@@ -4924,38 +4921,38 @@
         <v>401</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A168" s="1" t="s">
-        <v>0</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="B168" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C168" s="1">
         <v>1</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D168" s="1" t="s">
-        <v>3</v>
+        <v>402</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C169" s="1">
         <v>1</v>
@@ -4964,18 +4961,18 @@
         <v>402</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C170" s="1">
         <v>1</v>
@@ -4984,18 +4981,18 @@
         <v>402</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C171" s="1">
         <v>1</v>
@@ -5004,18 +5001,18 @@
         <v>402</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C172" s="1">
         <v>1</v>
@@ -5024,18 +5021,18 @@
         <v>402</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C173" s="1">
         <v>1</v>
@@ -5044,18 +5041,18 @@
         <v>402</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C174" s="1">
         <v>1</v>
@@ -5064,18 +5061,18 @@
         <v>402</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C175" s="1">
         <v>1</v>
@@ -5084,30 +5081,10 @@
         <v>402</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C176" s="1">
-        <v>1</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Faculties/Law/Undergrad Modules Law.xlsx
+++ b/Faculties/Law/Undergrad Modules Law.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Law\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BD7586-DD65-4623-BCEB-04B3589DD406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA53A12A-4D1C-42A1-A583-74F28C4B0ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12084" yWindow="2064" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4907,7 +4907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>367</v>
       </c>

--- a/Faculties/Law/Undergrad Modules Law.xlsx
+++ b/Faculties/Law/Undergrad Modules Law.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Law\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Law/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA53A12A-4D1C-42A1-A583-74F28C4B0ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{EA53A12A-4D1C-42A1-A583-74F28C4B0ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71DC0CB9-CCB9-4734-8571-08AFADF79716}"/>
   <bookViews>
-    <workbookView xWindow="12084" yWindow="2064" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="674">
   <si>
     <t>Module Code</t>
   </si>
@@ -1234,6 +1234,819 @@
   </si>
   <si>
     <t>AdvDip Labour Law 7311</t>
+  </si>
+  <si>
+    <t>Learning Outcome</t>
+  </si>
+  <si>
+    <t>Credits</t>
+  </si>
+  <si>
+    <t>Main Content</t>
+  </si>
+  <si>
+    <t>Interpret civil procedure structure in social transformation; compare philosophies; describe historical development; analyze procedural law controversies and construct related arguments.</t>
+  </si>
+  <si>
+    <t>Capita selecta including: underlying principles; historical evolution; advanced jurisdictional questions; special procedures; and the impact of the Constitution</t>
+  </si>
+  <si>
+    <t>Interpret criminal procedure concepts under Constitutional influence; compare philosophies; interpret selected controversies; construct defence and prosecutorial arguments; and interpret relationships with human rights.</t>
+  </si>
+  <si>
+    <t>Capita selecta including: underlying principles; historical evolution; complex bail questions; plea/sentence bargaining; punishment/sentencing; and the impact of the Constitution</t>
+  </si>
+  <si>
+    <t>Formulate arguments using administrative law principles and statutes; critically analyse case law; and evaluate public power exercise and its role in Africanisation and Ubuntu.</t>
+  </si>
+  <si>
+    <t>Body of law governing public power; court deference; defining administrative action; just administrative action under section 33; PAJA; judicial review; and social transformation</t>
+  </si>
+  <si>
+    <t>Discuss social transformation through Africanisation, decolonisation, and constitutionalisation; analyse and interpret public law fields in relation to the constitution.</t>
+  </si>
+  <si>
+    <t>Capita selecta including: constitutional history/theory; Comparative Constitutional Law; minority rights; elections; federalism; language rights; and Indigenous rights</t>
+  </si>
+  <si>
+    <t>Identify appropriate dispute resolution mechanisms; distinguish between types; explain steps and party roles; and explain mechanisms used in the African context.</t>
+  </si>
+  <si>
+    <t>Conciliation; mediation processes; arbitration processes and awards; the role of the mediator and arbitrator; and ADR in the African context</t>
+  </si>
+  <si>
+    <t>Demonstrate use of various listening and note-taking strategies, understanding of group dynamics, and analytical/critical thinking; apply critical and analytical reading skills, write well-constructed assignments/essays, and utilize IT-based productivity tools.</t>
+  </si>
+  <si>
+    <t>Listening and note-taking skills; group dynamics skills; critical thinking skills; reading/writing/referencing skills; and digital information literacy</t>
+  </si>
+  <si>
+    <t>Demonstrate note-taking and study methods; apply basic IT skills for law sources; find and summarize legal texts; solve legal problems via primary/secondary sources; and execute basic numerical calculations.</t>
+  </si>
+  <si>
+    <t>Basic research skills; legal writing genres (opinions, heads of argument); study skills; information technology; and numeracy skills</t>
+  </si>
+  <si>
+    <t>Demonstrate note-taking and study methods; apply IT skills for law sources; summarize legal texts; solve legal problems via essays; develop legal arguments; and execute numerical calculations.</t>
+  </si>
+  <si>
+    <t>Basic research skills; legal writing (opinions, demand letters); study skills (time management, plagiarism); IT skills; and finding statutes and living customs</t>
+  </si>
+  <si>
+    <t>Recognize the importance of statistics in private/public sectors; summarize and visualize basic data; and prepare/interpret simple statistical analyses using computer tools.</t>
+  </si>
+  <si>
+    <t>Visualization of statistics; regression analysis procedures; probability; sampling and distributions; and inferential statistics for business</t>
+  </si>
+  <si>
+    <t>Critically assess comparative law methodology; identify differences between SA and US legal systems; and perform critical comparative analysis of contemporary problems.</t>
+  </si>
+  <si>
+    <t>Comparative law methodology; introduction to the US legal system; and contemporary problems such as race, bioethics, and the law</t>
+  </si>
+  <si>
+    <t>Understand current SA child justice legislation and its socio-political context; evaluate child institutions and diversion services; and explain child justice theories and constitutional law.</t>
+  </si>
+  <si>
+    <t>International child justice rules; the Child Justice bill; police procedures; court procedures; diversion theory; restorative justice; and sentencing practice</t>
+  </si>
+  <si>
+    <t>Explain the judicial system; describe jurisdiction; distinguish actions from applications; evaluate trial preparation; assess costs; and describe the Constitution’s influence.</t>
+  </si>
+  <si>
+    <t>Role of civil procedure; sources; court officials; jurisdiction; summons and application procedures; defended actions; judgments; costs; execution; rescission; and pleadings drafting</t>
+  </si>
+  <si>
+    <t>Litigate constitutional matters and draft pleadings; identify interpretive arguments; explain Superior Court jurisdiction and powers; and discuss rights infringement resolution.</t>
+  </si>
+  <si>
+    <t>Core aspects of constitutional litigation including: access; standing; mootness; jurisdiction; interpretation; limitation analysis; and remedies</t>
+  </si>
+  <si>
+    <t>Apply consultation techniques (uBuntu); demonstrate drafting and negotiating; assess trial advocacy; express arguments; apply substantive law; and manage office skills.</t>
+  </si>
+  <si>
+    <t>Client-centred interviewing; diversity training; trial advocacy; lawyer-client dynamics; file structures; pleadings drafting; case theory; and preparing bills of costs</t>
+  </si>
+  <si>
+    <t>Describe the place of conflicts of law; evaluate its logic; develop legal arguments; apply principles to social transformation; and differentiate branch connections.</t>
+  </si>
+  <si>
+    <t>General principles: intro/theories; characterisation; renvoi; proof of foreign law; choice of law; law of domicile; jurisdiction; and enforcement of foreign judgements</t>
+  </si>
+  <si>
+    <t>Understand offer and acceptance; explain contract basis and mistake; investigate delicts and remedies; explain the transformative role of the Constitution; and draft basic contracts.</t>
+  </si>
+  <si>
+    <t>General principles/policies; constitutional values (fairness, legality); transformative constitutionalism; mistake; misrepresentation; remedies; duress; capacity; breach; and termination</t>
+  </si>
+  <si>
+    <t>Examine boundaries with other law branches; evaluate contractual justice; analyze the Constitution's impact; explain ubuntu and African Customary Law of Contract; and draft contracts.</t>
+  </si>
+  <si>
+    <t>Relationships with other private law; Consumer Protection Act; restraint of trade; error; writing and formalities; African Customary Law of Contract; and drafting</t>
+  </si>
+  <si>
+    <t>Understand Deeds Office procedures; draft powers of attorney and deeds; explain practical aspects and calculate transfer duty; and understand ownership statutes.</t>
+  </si>
+  <si>
+    <t>Deeds Office procedures; drafting documents; transfer duty calculations; property transfer from deceased estates; mortgage bonds; and sectional titles</t>
+  </si>
+  <si>
+    <t>Discuss Constitutional values/principles; explain the making of the Constitution and its role in decolonisation; evaluate government structure and Bill of Rights application.</t>
+  </si>
+  <si>
+    <t>Basic principles; historical survey; decolonisation and transformation; transformative constitutionalism; government structure; Bill of Rights; and Customary Law</t>
+  </si>
+  <si>
+    <t>Analyse business entities concepts in social transformation; describe foundational principles and statutes for entity formation; resolve practical problems; and explain management.</t>
+  </si>
+  <si>
+    <t>SA business entities (companies, CCs, trusts, partnerships); legal personality; pre-/post-incorporation contracts; shares; governance; finance; business rescue; and liquidation</t>
+  </si>
+  <si>
+    <t>Master fundamental rules and concepts of SA Company Law; understand procedures for entity formation and company management/administration.</t>
+  </si>
+  <si>
+    <t>Company law and the law relating to close corporations; capita selecta from advanced company law</t>
+  </si>
+  <si>
+    <t>Identify competition regulation principles; demonstrate knowledge of justifications/policy in social transformation; and explore Africanisation in market de-concentration.</t>
+  </si>
+  <si>
+    <t>History/policy; Competition Act and Amendment Bill; economics; restrictive practices (horizontal/vertical); abuse of dominance; mergers (digital environment); and jurisdiction</t>
+  </si>
+  <si>
+    <t>Identify and critique theoretical assumptions about law’s role in transforming post-colonial society, focusing on migration and spatial justice.</t>
+  </si>
+  <si>
+    <t>Underlying theoretical assumptions; history/development of Critical Theory and Critical Legal Theory; and theories of social justice/transformation</t>
+  </si>
+  <si>
+    <t>Identify differences in SA and US criminal justice; evaluate plea bargaining, legal representation, sentencing, and incarceration; and assess death penalty policies.</t>
+  </si>
+  <si>
+    <t>Delivery of defense services; plea-bargaining; sentencing; corrections; policing; administration of justice; prosecuting authority; and rights of legal representation</t>
+  </si>
+  <si>
+    <t>Discuss structure and concepts; describe historical development and Constitution impact; evaluate criminal liability; and discuss fundamental values like legality.</t>
+  </si>
+  <si>
+    <t>General principles of criminal law; selected offences; Constitution influence; criminal law in Africa; and reading/analytical skills development</t>
+  </si>
+  <si>
+    <t>Discuss structure and concepts in Africanisation context; demonstrate critical knowledge of history and impact of the Constitution; and analyse criminal law controversies.</t>
+  </si>
+  <si>
+    <t>Capita selecta from the fields of criminal law and criminology</t>
+  </si>
+  <si>
+    <t>Explain agency elements and sources of power; discuss duties and principal-agent relationships; solve practical problems; and identify negotiable instruments.</t>
+  </si>
+  <si>
+    <t>Agency (sources, duties, termination); Cession (effect, securitatem debiti); and Payment Instruments (negotiable instruments, signatures, liabilities, electronic fund transfers)</t>
+  </si>
+  <si>
+    <t>Identify foundational values of the Constitution and customary law; discuss the impact of the Bill of Rights; and identify constitutional developments affecting customary rules.</t>
+  </si>
+  <si>
+    <t>Application/Nature of Customary Law; values; Bill of Rights relationship; Traditional Leadership; Women; Children; Marriage and succession; and Property Rights/Land</t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of concepts in Africanisation context; explain transformative impact of the Constitution; and distinguish fault and strict liability.</t>
+  </si>
+  <si>
+    <t>Delict and the Constitution; multicultural society; elements of a delict; strict and vicarious liability; remedies; apportionment; and statutory compensation</t>
+  </si>
+  <si>
+    <t>Demonstrate an informed understanding of basic microeconomic theory and awareness of how the economy works at the micro level.</t>
+  </si>
+  <si>
+    <t>Demand and supply; elasticities; efficiency and equity; consumer behavior; firm behavior (profit/cost); market structures; and market failure</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of how the various sectors of the economy interrelate using basic macroeconomic tools and theories.</t>
+  </si>
+  <si>
+    <t>The macroeconomic problem; circular flow of income; national income accounting; aggregate D/S; unemployment; money/banking; inflation; and policy</t>
+  </si>
+  <si>
+    <t>Explain and apply microeconomic principles within consumer theory, producer theory, and market structures; apply mathematical tools for analysis.</t>
+  </si>
+  <si>
+    <t>Consumer behavior; individual and market demand; production theory; costs; profit maximisation; and market power (monopoly/monopsony)</t>
+  </si>
+  <si>
+    <t>Apply macroeconomic theory to SA issues; construct graphs and equations for macro concepts; and explain domestic and global developments.</t>
+  </si>
+  <si>
+    <t>National Income; components of GDP; Goods and Financial Market; IS-LM model; labour market; and AS-AD model</t>
+  </si>
+  <si>
+    <t>Apply differentiation to solve non-linear economic problems; solve macro linear problems; explain matrix concepts; and apply integral calculus.</t>
+  </si>
+  <si>
+    <t>Differentiation techniques; macro linear problems (AD-AS, IS-LM); micro non-linear problems (equilibrium); matrices; and integral calculus</t>
+  </si>
+  <si>
+    <t>Explain the theoretical background of econometrics; apply basic math/stats tools to economic relationships; and use quantitative software.</t>
+  </si>
+  <si>
+    <t>Theoretical background; analytical tools for relationships; functional forms for models; and mathematical/statistical analysis of data</t>
+  </si>
+  <si>
+    <t>Conduct multivariate regression analysis and inference tests; explain regression models with dummy variables and CLRM violations.</t>
+  </si>
+  <si>
+    <t>Detailed Main Content for Part 4 - consult department syllabus</t>
+  </si>
+  <si>
+    <t>Explain and apply general equilibrium and welfare analysis; analyse behaviour under monopolistic competition/oligopoly; and use game theoretic models.</t>
+  </si>
+  <si>
+    <t>Market structure; competitive strategy; pricing with market power; game theory; general equilibrium; and asymmetric information</t>
+  </si>
+  <si>
+    <t>Explain long-term economic growth (capital, labour, tech); model prices/inflation/unemployment in open economies; and evaluate macro policies.</t>
+  </si>
+  <si>
+    <t>Long run growth; growth, saving and technology; expectations in financial markets; and fiscal, monetary, and exchange rate policies</t>
+  </si>
+  <si>
+    <t>Discuss the composition of the SA public sector; analyse the role of government and market failure; and apply expenditure/tax theory.</t>
+  </si>
+  <si>
+    <t>Composition of public sector; views on government role; market failure; bureaucratic failure; taxation principles; and fiscal policy</t>
+  </si>
+  <si>
+    <t>Information on detailed outcomes and main content for ECO335 is currently restricted - consult EMS Department.</t>
+  </si>
+  <si>
+    <t>Main content restricted - consult EMS Department</t>
+  </si>
+  <si>
+    <t>Model foundational concepts of development economics; critically analyse patterns of developing countries; and analyse statistical data.</t>
+  </si>
+  <si>
+    <t>Determination of poverty and inequality; growth experiences; agrarian change; industrialization strategies; and capital flows</t>
+  </si>
+  <si>
+    <t>Demonstrate English language communicative competence and academic literacy skills (writing, reading, listening, speaking) within a legal context.</t>
+  </si>
+  <si>
+    <t>Material includes: the Constitution; films, graphics, fiction/journalism on law and morality; legal articles; and legal textbooks</t>
+  </si>
+  <si>
+    <t>Apply substantive law to scenarios; draft legal documents to establish ventures (MOIs, trust deeds); apply negotiation skills; and communicate with hypothetical clients.</t>
+  </si>
+  <si>
+    <t>Sole Proprietorships; Partnerships; Trusts; Companies; Charitable vehicles; and Intellectual Property</t>
+  </si>
+  <si>
+    <t>Demonstrate skills in reading, writing, speaking and listening; contextualise, identify, and critically analyse English language and literature texts.</t>
+  </si>
+  <si>
+    <t>Selection of contemporary texts (visual and print-based); figures of speech and metaphor; and reflection on language issues in society</t>
+  </si>
+  <si>
+    <t>Understand and apply the process of critical analysis to a variety of historical and contemporary English language and literature texts.</t>
+  </si>
+  <si>
+    <t>Selection of texts from different historical periods/regions; narrative techniques and genres; and poetry, drama and prose techniques</t>
+  </si>
+  <si>
+    <t>Refer to Faculty of Arts and Humanities Calendar for outcomes.</t>
+  </si>
+  <si>
+    <t>Selected works of poetry and prose from SA, Africa, and the Diaspora providing insight into culture, identity and postcolonial transformation</t>
+  </si>
+  <si>
+    <t>Information on detailed outcomes and main content for ENG221 is currently restricted - consult Arts and Humanities Department.</t>
+  </si>
+  <si>
+    <t>Main content restricted - consult Arts and Humanities Department</t>
+  </si>
+  <si>
+    <t>Content presupposes an understanding of the significance of nineteenth-century literature covered in ENG221</t>
+  </si>
+  <si>
+    <t>Postmodernism (theoretical/creative material); Postcolonial studies (developing world, slavery, colonialism); and world literature from readers/films</t>
+  </si>
+  <si>
+    <t>Evaluate law/policy and Constitution impact on the "environment"; examine ethical duties; evaluate sustainable development; and identify environmental racism.</t>
+  </si>
+  <si>
+    <t>Nature/scope of environmental law; global and human rights dimensions; land use/planning; biological diversity; climate change; and environmental justice</t>
+  </si>
+  <si>
+    <t>Explain the meaning and significance of basic ethical concepts (morality, meta-ethics) and ethical questions concerning virtues and the good society.</t>
+  </si>
+  <si>
+    <t>Understand rationale for regional integration (SADC, AU, EU); demonstrate relationship between legal systems; and analyse impact on citizen rights.</t>
+  </si>
+  <si>
+    <t>History/institutions of SADC, AU, and EU; sources of EU Law; Members’ Municipal legal systems; fundamental freedoms; and trade agreement topics</t>
+  </si>
+  <si>
+    <t>Construct a position based on evidence; analyze situations for legal solutions in social transformation/Africanisation; and demonstrate fact understanding.</t>
+  </si>
+  <si>
+    <t>Functions of evidence law; admissibility; unconstitutionally obtained evidence; hearsay; admissions/confessions; evidence types; and the burden of proof</t>
+  </si>
+  <si>
+    <t>Explain the impact of the Constitution on marriage/family; compare fundamental principles of civil and customary marriages and divorce.</t>
+  </si>
+  <si>
+    <t>Role of the Constitution; Engagement; valid civil/customary marriage requirements; consequences; Matrimonial Property Law; and parent-child relationships</t>
+  </si>
+  <si>
+    <t>Identify fundamental principles of civil and customary marriages and divorce in SA/Africa; and solve legal problems using social transformation approaches.</t>
+  </si>
+  <si>
+    <t>Role of the Constitution; Engagement requirements; valid marriage requirements; Matrimonial Property Law; dissolution (death/divorce); and parent-child relationships</t>
+  </si>
+  <si>
+    <t>Evaluate the evolving influence of the Constitution on family notions; analyse family forms; and solve problems in social transformation context.</t>
+  </si>
+  <si>
+    <t>Impact of the Constitution; unions (civil, domestic partnerships, customary); mediation; domestic violence; parent-child relationship; ART and surrogacy</t>
+  </si>
+  <si>
+    <t>Define/explain introductory concepts in sociolinguistics and forensic linguistics; and understand its evolution as a scientific discipline.</t>
+  </si>
+  <si>
+    <t>Forensic linguistic issues in multilingual societies; court record languages; role of language in law; and courtroom genres</t>
+  </si>
+  <si>
+    <t>Courtroom discourse and intercultural communication; forensic expert witnesses; language as evidence; and forensic expertise case studies</t>
+  </si>
+  <si>
+    <t>Investigative analysis of text; forensic plagiarism and detection</t>
+  </si>
+  <si>
+    <t>Analyse context and complexities of monolingual vs multilingual policies in the Criminal Justice System; and evaluate police record construction.</t>
+  </si>
+  <si>
+    <t>(Mis)representation of police evidence in the courtroom</t>
+  </si>
+  <si>
+    <t>Define and apply elements of the accounting equation; record transactions; and apply accrual accounting adjustments to pre-adjustment trial balances.</t>
+  </si>
+  <si>
+    <t>Evaluate an entity’s financial strategies/goals; analyse financial situation; comprehend risk/return; and calculate cost of capital.</t>
+  </si>
+  <si>
+    <t>Discuss investment environment/process; explain standard investment concepts; and analyse risk/return features of selected securities.</t>
+  </si>
+  <si>
+    <t>Security and fundamental analysis; mutual funds; asset allocation models; popular index models; and portfolio performance measurement</t>
+  </si>
+  <si>
+    <t>Calculate, analyse and evaluate investment, financing and dividend decisions relating to an entity and its activities.</t>
+  </si>
+  <si>
+    <t>Valuations; Capital Budgeting; working capital management; Cost of Capital; Capital structure; and Financing/Dividend decisions</t>
+  </si>
+  <si>
+    <t>Refer to Faculty of Economic and Management Sciences Calendar for outcomes.</t>
+  </si>
+  <si>
+    <t>Provide in-depth analysis of company performance using key data; identify strengths/weaknesses; and recommend actions to address them.</t>
+  </si>
+  <si>
+    <t>Discuss international financial architecture and BoP accounts; and explain how consumer/firm/government decisions affect them.</t>
+  </si>
+  <si>
+    <t>Discuss feminist thinkers; analyse women's rights under national/international instruments; and evaluate patriarchal designs within African context.</t>
+  </si>
+  <si>
+    <t>Feminist thinking; critical perspectives on women’s rights in Africa; equality and non-discrimination; sexuality and gender; and impacts of custom/culture</t>
+  </si>
+  <si>
+    <t>Analyse international business law concepts; discuss international trade institutions and conventions; and advise on trade across borders for scenarios.</t>
+  </si>
+  <si>
+    <t>International trade framework (UN, WTO); sales transactions; CISG; Incoterms; FDI regulation; dispute resolution (arbitration); and developing country challenges</t>
+  </si>
+  <si>
+    <t>Understand basic micro/macro principles; the role of producers/consumers/government; and basic international trade and globalisation.</t>
+  </si>
+  <si>
+    <t>Modern economic thought; economic problem and decision making; supply and demand; economic systems; SA economy; and global trade</t>
+  </si>
+  <si>
+    <t>Discuss social transformation through Africanisation; explain SA law history; list sources; and discuss legal philosophy debates and African jurisprudence.</t>
+  </si>
+  <si>
+    <t>History (pre-colonial to democratic); legal system relationships; impact of the Constitution; social change theories; separation of powers; and formal sources</t>
+  </si>
+  <si>
+    <t>Discuss transformation through Africanisation; define the concept of law; explain SA law history; and discuss government structures in terms of the Constitution.</t>
+  </si>
+  <si>
+    <t>History of SA legal system; impact of the Constitution; social change theories; separation of powers; branches of law; and law in the global economy</t>
+  </si>
+  <si>
+    <t>Discuss social transformation through Africanisation; identify divisions of SA law; identify business world law operations; and list civil/criminal procedures.</t>
+  </si>
+  <si>
+    <t>Private law outline; law and business; civil procedure; criminal law/procedure; law of evidence; courts vs ADR; and the legal profession/ethics</t>
+  </si>
+  <si>
+    <t>Discuss transformation through Africanisation; identify areas of law; discuss selected concepts in context; and list differences between courts and ADR.</t>
+  </si>
+  <si>
+    <t>Private law outline; law and the business world; civil and criminal procedure; law of evidence; courts vs ADR; and the legal profession</t>
+  </si>
+  <si>
+    <t>Explain insolvency principles in SA/Africa; apply principles to surrender, sequestration, and rehabilitation; and engage in legal research and writing.</t>
+  </si>
+  <si>
+    <t>Historical background; voluntary surrender; compulsory sequestration; trustee functions; rehabilitation; juristic person liquidation; and Constitution impact</t>
+  </si>
+  <si>
+    <t>Analyse Internet law concepts in social transformation; explain personal info protection, online contracts, copyright, and cybercrime laws.</t>
+  </si>
+  <si>
+    <t>Internet workings/law intro; personal info and interception; electronic contracts; consumer protection; trademarks/domain names; taxation of E-Commerce; and cybercrime</t>
+  </si>
+  <si>
+    <t>Analyse founding theories; identify Intellectual Property forms; discuss global regime debates; and discuss traditional knowledge protection (Africanisation).</t>
+  </si>
+  <si>
+    <t>Founding theories; Copyright Law; Patent Law and Industrial Designs; Trade Mark Law and Unlawful Competition; and Traditional Knowledge protection</t>
+  </si>
+  <si>
+    <t>Understand the meaning of work and career concepts; explain life and career stages; and explain organizational and individual roles in development.</t>
+  </si>
+  <si>
+    <t>Career Choice; Career Anchors; stages; organizational support; and implications of organizational changes for careers</t>
+  </si>
+  <si>
+    <t>Psych assessment techniques (nature, application, abuse); multimodal methods; and legislative/ethical frameworks for testing</t>
+  </si>
+  <si>
+    <t>Recall/explain history of HRM and major functions of an HR department; and apply HR knowledge to real-life simulated scenarios.</t>
+  </si>
+  <si>
+    <t>Job analysis/design; recruitment and induction; internal staffing; performance management; and career development</t>
+  </si>
+  <si>
+    <t>Describe environmental context of labour relations; and explain roles of various parties and the importance of sound relations in SA.</t>
+  </si>
+  <si>
+    <t>Understand trace historical development of Organizational Behaviour; discuss theories of motivation/leadership; and evaluate technology impacts.</t>
+  </si>
+  <si>
+    <t>Define consumer behavior; describe market segmentation and Marketing concept; and describe consumer research and decision-making processes.</t>
+  </si>
+  <si>
+    <t>Discuss transformation through Africanisation; reflect on law/morality relationships; and explain philosophical foundations used in SA adjudication.</t>
+  </si>
+  <si>
+    <t>Law vs Western modernity/colonialism; law vs morality/politics; law vs transformation/critique; and critical engagement with academic texts</t>
+  </si>
+  <si>
+    <t>Explain basic labour law principles; assess controversial issues under the Constitution; and understand employment condition negotiation/dispute resolution.</t>
+  </si>
+  <si>
+    <t>Individual employment law; collective bargaining law; industrial action; dispute resolution; and transformation via ideals of Africanisation/decolonisation</t>
+  </si>
+  <si>
+    <t>Explain relevance of access to justice; apply logic/technology principles; appraise digital decision-making systems; and test entitlement processes.</t>
+  </si>
+  <si>
+    <t>Access to justice legal/practical aspects; digitalisation; legal logic; digital systems building on existing labour law knowledge; and procedure digitalisation</t>
+  </si>
+  <si>
+    <t>Demonstrate understanding of current debates in labour law; describe pratique issues; and conduct research on specific labour areas.</t>
+  </si>
+  <si>
+    <t>Atypical employment; business restructuring; dismissal law issues; discrimination law; collective bargaining; common law resurgence; and dispute resolution</t>
+  </si>
+  <si>
+    <t>Identify applicable rules/procedures; identify procedures within criminal law; draft documents (Bail Affidavits); and review a live bail application.</t>
+  </si>
+  <si>
+    <t>Criminal justice principles/sanctions; application in SA criminal courts; value and impact of the Constitution; and authentic court exposure (WIL)</t>
+  </si>
+  <si>
+    <t>Identify causes/effects of economic criminality; comprehend legal/institutional frameworks; and develop prevention and eradication recommendations.</t>
+  </si>
+  <si>
+    <t>Impact on socio-economic rights; Money laundering stages/prosecution; Corruption forms and mutual assistance; and recovery of lost assets</t>
+  </si>
+  <si>
+    <t>Discuss colonial/apartheid land holding history; apply Constitutional property clause to land reform and housing; and discuss customary land tenure.</t>
+  </si>
+  <si>
+    <t>SA land tenure system overview; land and housing reform; restitution/redistribution; constitutional property law; and customary land tenure systems</t>
+  </si>
+  <si>
+    <t>Identify valid insurance policies; apply materiality tests for misrepresentation; and analyse scenarios using legislation/Constitution for resolution.</t>
+  </si>
+  <si>
+    <t>Requirements for valid insurance; policy interpretation; insurable interest; risk; misrepresentation/non-disclosure; and insurance digitisation</t>
+  </si>
+  <si>
+    <t>List/compare fundamental concepts of common law and customary law principles; identify legislation/case law influence; and discussing legal problems.</t>
+  </si>
+  <si>
+    <t>Law of Persons and Constitution; terminology; beginning/end of subjectivity; status factors (age, domicile, birth, addiction,curatorship); and customary law status</t>
+  </si>
+  <si>
+    <t>Identify common law and customary law principles; identify applicable legislation and Constitution influence; and solve problems via research techniques.</t>
+  </si>
+  <si>
+    <t>Law of Persons and Constitution; legal subjectivity (unborn fetus); end of subjectivity; and factors influencing status (mental illness, prodigality, insolvency)</t>
+  </si>
+  <si>
+    <t>Illustrate transformative constitutionalism in indigenous laws; evaluate legal pluralism as product of colonisation; and explain future legal behavior adaptation.</t>
+  </si>
+  <si>
+    <t>Philosophical context of pluralism; impact of colonial rule; Muslim Personal Law; Customary law critique; communal vs individual dissonance; and legal identity</t>
+  </si>
+  <si>
+    <t>Apply consultation techniques (uBuntu) in simulations; assess trial advocacy approaches; and express arguments effectively (oral/written).</t>
+  </si>
+  <si>
+    <t>Simulated environment communication; basic trial advocacy; consultation techniques; diversity training; and capita selecta (civil procedure, gender law, ethics)</t>
+  </si>
+  <si>
+    <t>Explain context of SA business; internal/external factors; success management principles; articulated business research; and plan/work effectively in teams.</t>
+  </si>
+  <si>
+    <t>Business enterprise as system; Management history; Entrepreneurship; establishment; managing functional areas (marketing, finance, etc.); and POLC functions</t>
+  </si>
+  <si>
+    <t>Describe entrepreneurship field development; discuss policies to alleviate challenges; and demonstrate understanding of small enterprise requirements.</t>
+  </si>
+  <si>
+    <t>Venture creation processes; lifecycle; case studies of SA entrepreneurs; and developing business plans</t>
+  </si>
+  <si>
+    <t>Demonstrate understanding of different finance requirements across entrepreneurial life cycle; and identify SME financing opportunities.</t>
+  </si>
+  <si>
+    <t>Define marketing and outline process steps; and discuss customer relationship management and customer-driven strategy elements.</t>
+  </si>
+  <si>
+    <t>Information on detailed outcomes and main content for MAN233 is currently restricted - consult EMS Department.</t>
+  </si>
+  <si>
+    <t>Critically analyse the nature of services; distinguish product and services; and evaluate marketing improvements.</t>
+  </si>
+  <si>
+    <t>Understand strategic management principles; analyse business environment; identify capabilities/gaps; and formulate realistic strategies for case studies.</t>
+  </si>
+  <si>
+    <t>Mission, vision, objectives; strategic choice; Environment Analysis; Strategy formulation/implementation; and Strategy control</t>
+  </si>
+  <si>
+    <t>Apply communication theory; describe business models; construct communication; design data collection instruments; and analyse primary/secondary data.</t>
+  </si>
+  <si>
+    <t>Communication theory; Audio-visual presentations; Formal written communication; Data management and analysis; and literature reviews</t>
+  </si>
+  <si>
+    <t>Define project management and evolving roles; articulate project life cycle stages; and identify required resources/stakeholders.</t>
+  </si>
+  <si>
+    <t>Identify and explain the central ideas of the philosopher(s) discussed in the module.</t>
+  </si>
+  <si>
+    <t>Identify/explain central ideas of major value theories and core arguments; and respond critically to theories in contemporary moral contexts.</t>
+  </si>
+  <si>
+    <t>Introductory moral and political philosophy; and challenging contemporary issues</t>
+  </si>
+  <si>
+    <t>Understand nature of philosophical questions; and critically analyse problems in ethics, epistemology, ontology and religious belief.</t>
+  </si>
+  <si>
+    <t>Understand/engage with primary texts; identify/compare major ethical theories; and critically engage with supporting arguments.</t>
+  </si>
+  <si>
+    <t>Investigation of nature of moral reasons; and contemporary questions on moral reason existence</t>
+  </si>
+  <si>
+    <t>Identify/explain central ideas of epistemological theories and core arguments; and apply emerging theories to solutions for challenges.</t>
+  </si>
+  <si>
+    <t>Foundations of knowledge (rationalist/empiricist traditions); critical responses; and current developments in theory of knowledge</t>
+  </si>
+  <si>
+    <t>Demonstrate critical understanding of nature/relationships of 'race', 'culture' and 'identity'; and locate concepts in speech and text.</t>
+  </si>
+  <si>
+    <t>Assess record-keeping in practice via technology; explain administration of deceased estates; and resolve ethical problems in professional contexts.</t>
+  </si>
+  <si>
+    <t>Legally relevant numeracy/accountancy; ethics and practice management; Deceased Estates; Personal Injury Claims; and the Legal Practice Act</t>
+  </si>
+  <si>
+    <t>Identify/describe characteristics of politics and the state (authority, power, etc.); outline political institutions; and understand IR theoretical foundations.</t>
+  </si>
+  <si>
+    <t>Explain terminology/trends of public administration; and compare structure/theories/systems of governance in developed/developing nations.</t>
+  </si>
+  <si>
+    <t>Describe key moments in African history (IR/IPE perspective); and identify contemporary key actors and issues on the African continent.</t>
+  </si>
+  <si>
+    <t>Demonstrate an informed understanding of the structure and function of psychology.</t>
+  </si>
+  <si>
+    <t>Main content restricted - consult CHS Department</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>Refer to Faculty of Community and Health Sciences Calendar for outcomes.</t>
+  </si>
+  <si>
+    <t>Critically analyse conception of typical/atypical behaviour in SA settings; and analyse sociocultural/historical frameworks and power dynamics.</t>
+  </si>
+  <si>
+    <t>Describe the meaning of Public International Law in African/global contexts; explain sources and principles; evaluate subject recognition; and adjudicate contentious proceedings.</t>
+  </si>
+  <si>
+    <t>Theory and sources (custom, treaty); SA constitutional context; subjects of PIL (statehood); jurisdiction and crimes; state responsibility; United Nations role; and self-defence</t>
+  </si>
+  <si>
+    <t>Demonstrate understanding of number systems; knowledge to work with integers/rational numbers; and solve basic arithmetic problems.</t>
+  </si>
+  <si>
+    <t>Supply/demand graphs; exponential and logarithmic equations and graphs linked to finance; and descriptive statistics</t>
+  </si>
+  <si>
+    <t>Submit a feasible research topic; conduct literature reviews; design a project; and utilise appropriate ethical considerations when conducting research.</t>
+  </si>
+  <si>
+    <t>Research methods and analysis; ethical considerations; research proposals; and the creation of a publishable research article (5000-6000 words)</t>
+  </si>
+  <si>
+    <t>Describe demands of legal research in post-colonial Africa; identify problems; conduct literature reviews (Africanisation); and construct research proposals.</t>
+  </si>
+  <si>
+    <t>Research process components; question development; strategies; IT use; methodologies (historical, interdisciplinary); and theoretical considerations</t>
+  </si>
+  <si>
+    <t>Explain scope and content of Rights; apply the limitations clause and remedies; identifyviolations; and formulate arguments based on research.</t>
+  </si>
+  <si>
+    <t>Fundamental rights to address inequities; transformative constitutionalism; law/politics intersection; and globalisation/digitalisation influence</t>
+  </si>
+  <si>
+    <t>Explain common law principles of sale and lease; identify remedies; list party duties; and analyse the Constitution's impact on eviction rights.</t>
+  </si>
+  <si>
+    <t>Essentialia of sale and lease; party duties; remedies; termination; Relations with third parties; PIE Act; and the Rental Housing Act</t>
+  </si>
+  <si>
+    <t>Understand rhetorical effects of mass media and literature texts; undertake in-depth genre analyses; and analyse text structure/context.</t>
+  </si>
+  <si>
+    <t>Focus on the concept "text" and various textual forms; rhetorical skills in construction; and meaning of discourse analysis</t>
+  </si>
+  <si>
+    <t>Identify and analyse linguistic and narrative strategies in variety of texts; understand text as construct; and understand language choices/cohesion.</t>
+  </si>
+  <si>
+    <t>Define/explain the need for access to social security; understand relationship between statutory and Indigenous systems; and critically analyse schemes in 4IR.</t>
+  </si>
+  <si>
+    <t>Sources/administration of social security law; schemes (UIF, assistance, pensions); Indigenous systems; and changing work in the Fourth Industrial Revolution</t>
+  </si>
+  <si>
+    <t>Identify/apply canons of statutory interpretation; evaluate linear and holistic interpretation methods; and compile legislative or drafting histories.</t>
+  </si>
+  <si>
+    <t>Statutory law as source under transformative constitution; legislative process; conflicts between statutes; interpretation canons; and research skills</t>
+  </si>
+  <si>
+    <t>Identify succession principles; evaluate the impact of constitutionalism on succession law; and divide intestate estates according to rules and precedent.</t>
+  </si>
+  <si>
+    <t>Administration of deceased estates; Intestate/Estate succession; testamentary capacity; execution formalities; condonation; Wills contents; and interpretion/rectification</t>
+  </si>
+  <si>
+    <t>Define/classify things; distinguish real rights; understand acquisition/protection/termination; and analyse the impact of Constitution section 25 and the PIE Act.</t>
+  </si>
+  <si>
+    <t>Introduction to Things; ownership; possession; servitudes; real security; and Constitutional Property Law</t>
+  </si>
+  <si>
+    <t>Evaluate basic trust law principles; explain development by courts; and analyse the utility/challenges of the trust in commercial practice.</t>
+  </si>
+  <si>
+    <t>creation/amendment/termination; legal position of trustee and beneficiary; sham trusts; alter ego trusts; public policy; and constitutionalism</t>
+  </si>
+  <si>
+    <t>Research and read income tax cases; apply the General Deduction Formula; solve problems in social transformation; and discuss decolonised income taxation.</t>
+  </si>
+  <si>
+    <t>Interpretation of statutes; definition of gross income; inclusions/deductions; taxation of trusts/companies; donation tax; and taxation in a digital environment</t>
+  </si>
+  <si>
+    <t>Appraise law of obligation concepts; apply principles in social transformation; and explain the impact of constitutionalism and public policy.</t>
+  </si>
+  <si>
+    <t>Enrichment idea history; liability requirements; condictiones; limited capacity liability; improvements; work/services; and Law/Constitution relationship</t>
+  </si>
+  <si>
+    <t>Understand/interpret rules of Xhosa sound system, word-formation and sentence construction; and take notes/write assignments.</t>
+  </si>
+  <si>
+    <t>Phonetics and Phonology; morphology; syntax; and skills (referencing, editorial, research, note-taking)</t>
+  </si>
+  <si>
+    <t>Appreciate and describe Xhosa culture and heritage; give account of development of Xhosa literature and oral cultures; and describe cultural contexts.</t>
+  </si>
+  <si>
+    <t>Describe principles of Administrative Justice (section 33); distinguish review from appeal; and explore grounds of Judicial Review.</t>
+  </si>
+  <si>
+    <t>Legality principle; section 33 requirements; Administrative Action validity; PAJA; and Locus Standi</t>
+  </si>
+  <si>
+    <t>Describe and explain elementary aspects of Criminal Law; identify and discuss the elements of various crimes.</t>
+  </si>
+  <si>
+    <t>General liability elements; inchoate crimes; participation; strict and vicarious liability; fraud; theft; corruption; and money laundering</t>
+  </si>
+  <si>
+    <t>Describe gathering evidence principles/procedures; apply presentation rules; and explain compellability of witnesses and judicial discretion.</t>
+  </si>
+  <si>
+    <t>Quantum of evidence; real and documentary evidence; hearsay rule; character evidence; right against self-incrimination; and spousal privilege</t>
+  </si>
+  <si>
+    <t>Explain internal vs external auditors; illustrate audit conduct; interpret Risk/Enterprise Risk Management; and discuss internal controls.</t>
+  </si>
+  <si>
+    <t>Organization of profession; ethics; business process analysis; risk analysis; compliance; and substantive tests of business processes</t>
+  </si>
+  <si>
+    <t>Identify anti-corruption compliance methods; apply loss-recovery techniques; and explain suspec interview info-gathering techniques.</t>
+  </si>
+  <si>
+    <t>Anti-Corruption Conventions; SA asset forfeiture (POCA); FICA; PCCA; fraud prevention; deception detection; and information obtainment techniques</t>
+  </si>
+  <si>
+    <t>Evaluate Employment contract operation; list duties of parties; identify dismissal grounds; and explain Protected Disclosures Act features.</t>
+  </si>
+  <si>
+    <t>Duties of parties; dismissal grounds; misconduct; unfair labour practices; Labour Relations Act; and the Protected Disclosures Act</t>
+  </si>
+  <si>
+    <t>Distinguish law from other mechanisms; explain judicial precedent; interpret legislation; and conduct basic research using varied sources.</t>
+  </si>
+  <si>
+    <t>Law concepts; pre-democratic systems relations; Constitution impact; court hierarchy/jurisdiction; social change theories; and separation of powers</t>
+  </si>
+  <si>
+    <t>Demonstrate note-taking/study methods (Africanisation context); summarize legal texts; solve problems via communications; and execute numerical calculations.</t>
+  </si>
+  <si>
+    <t>Basic research skills; legal writing (opinions, heads of argument); study skills; IT skills; and reading statutes and living customs</t>
+  </si>
+  <si>
+    <t>Understand Labour Law principles; understand Constitution transformation of labour law; understand condition negotiation and dispute resolution.</t>
+  </si>
+  <si>
+    <t>Historical development; SA Constitution; unfair dismissals; non-standard employment; 4IR; Collective Bargaining; and Dispute Resolution</t>
+  </si>
+  <si>
+    <t>Explain collective labour law principles; discuss work nature changes; and apply statutory provisions for business transfers.</t>
+  </si>
+  <si>
+    <t>Collective bargaining law; industrial action; dispute resolution; worker participation; Organisational Rights; and business transfer as a going concern</t>
+  </si>
+  <si>
+    <t>Explain principles for evaluation of unfair dismissals; explain common law role; and identify appropriate remedies for unfair practices.</t>
+  </si>
+  <si>
+    <t>common law vs dismissal role; misconduct/incapacity dismissals; remedies/compensation limits; operational requirements; automatically unfair dismissals; and non-standard employment</t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of conflict dynamics; apply skills for workplace conflict management; and apply resolution processes for disputes.</t>
+  </si>
+  <si>
+    <t>Statutory resolution institutions (CCMA, councils); SA labour law processes; preventing and managing workplace conflicts; and conciliation/arbitration/adjudication</t>
+  </si>
+  <si>
+    <t>Explain/apply substantive equality as enshrined in the Constitution; and apply EEA provisions relating to discrimination and affirmative action.</t>
+  </si>
+  <si>
+    <t>Substantive vs formal equality; direct/indirect discrimination; Sexual Harassment; burden of proof; Affirmative Action plans; and income inequality/differentials</t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of social security forms and link to labour rights; display knowledge of statutory provision application and enforcement.</t>
+  </si>
+  <si>
+    <t>Compensation for occupational injuries/diseases; Unemployment Insurance; workplace health/safety; pensions; retirement funds; and social assistance</t>
   </si>
 </sst>
 </file>
@@ -1580,34 +2393,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
     <col min="6" max="6" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G1" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1626,8 +2448,17 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1646,8 +2477,17 @@
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G3" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I3" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1666,8 +2506,17 @@
       <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G4" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I4" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1686,8 +2535,17 @@
       <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G5" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -1706,8 +2564,17 @@
       <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G6" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -1726,8 +2593,17 @@
       <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G7" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="I7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1746,8 +2622,17 @@
       <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G8" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -1766,8 +2651,17 @@
       <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G9" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I9" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -1786,8 +2680,17 @@
       <c r="F10" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G10" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I10" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -1806,8 +2709,17 @@
       <c r="F11" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G11" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
@@ -1826,8 +2738,17 @@
       <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G12" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -1846,8 +2767,17 @@
       <c r="F13" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G13" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I13" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
@@ -1866,8 +2796,17 @@
       <c r="F14" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G14" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -1886,8 +2825,17 @@
       <c r="F15" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G15" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I15" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -1906,8 +2854,17 @@
       <c r="F16" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G16" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I16" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
@@ -1926,8 +2883,17 @@
       <c r="F17" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G17" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I17" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -1946,8 +2912,17 @@
       <c r="F18" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G18" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I18" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -1966,8 +2941,17 @@
       <c r="F19" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G19" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
@@ -1986,8 +2970,17 @@
       <c r="F20" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G20" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="I20" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>54</v>
       </c>
@@ -2006,8 +2999,17 @@
       <c r="F21" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G21" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I21" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
@@ -2026,8 +3028,17 @@
       <c r="F22" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G22" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>58</v>
       </c>
@@ -2046,8 +3057,17 @@
       <c r="F23" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G23" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="I23" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>60</v>
       </c>
@@ -2066,8 +3086,17 @@
       <c r="F24" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G24" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I24" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>64</v>
       </c>
@@ -2086,8 +3115,17 @@
       <c r="F25" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G25" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="I25" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>67</v>
       </c>
@@ -2106,8 +3144,17 @@
       <c r="F26" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G26" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="I26" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>69</v>
       </c>
@@ -2126,8 +3173,17 @@
       <c r="F27" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G27" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>71</v>
       </c>
@@ -2146,8 +3202,17 @@
       <c r="F28" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G28" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I28" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>73</v>
       </c>
@@ -2166,8 +3231,17 @@
       <c r="F29" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G29" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I29" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>75</v>
       </c>
@@ -2186,8 +3260,17 @@
       <c r="F30" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G30" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I30" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>77</v>
       </c>
@@ -2206,8 +3289,17 @@
       <c r="F31" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G31" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I31" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>80</v>
       </c>
@@ -2226,8 +3318,17 @@
       <c r="F32" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G32" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="I32" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>82</v>
       </c>
@@ -2246,8 +3347,17 @@
       <c r="F33" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G33" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="I33" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>84</v>
       </c>
@@ -2266,8 +3376,17 @@
       <c r="F34" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G34" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I34" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>86</v>
       </c>
@@ -2286,8 +3405,17 @@
       <c r="F35" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G35" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="I35" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>88</v>
       </c>
@@ -2306,8 +3434,17 @@
       <c r="F36" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G36" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="I36" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>91</v>
       </c>
@@ -2326,8 +3463,17 @@
       <c r="F37" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G37" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="I37" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>93</v>
       </c>
@@ -2346,8 +3492,17 @@
       <c r="F38" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G38" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="I38" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>95</v>
       </c>
@@ -2366,8 +3521,17 @@
       <c r="F39" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G39" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="I39" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>97</v>
       </c>
@@ -2386,8 +3550,17 @@
       <c r="F40" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G40" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="I40" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>100</v>
       </c>
@@ -2406,8 +3579,17 @@
       <c r="F41" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G41" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I41" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>102</v>
       </c>
@@ -2426,8 +3608,17 @@
       <c r="F42" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G42" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I42" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
@@ -2446,8 +3637,17 @@
       <c r="F43" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G43" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="I43" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>106</v>
       </c>
@@ -2466,8 +3666,17 @@
       <c r="F44" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G44" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="I44" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>108</v>
       </c>
@@ -2486,8 +3695,17 @@
       <c r="F45" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G45" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="I45" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>110</v>
       </c>
@@ -2506,8 +3724,17 @@
       <c r="F46" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G46" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I46" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>112</v>
       </c>
@@ -2526,8 +3753,17 @@
       <c r="F47" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G47" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I47" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>115</v>
       </c>
@@ -2546,8 +3782,17 @@
       <c r="F48" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G48" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I48" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>117</v>
       </c>
@@ -2566,8 +3811,17 @@
       <c r="F49" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G49" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="I49" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>120</v>
       </c>
@@ -2586,8 +3840,17 @@
       <c r="F50" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G50" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="I50" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>122</v>
       </c>
@@ -2606,8 +3869,17 @@
       <c r="F51" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G51" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="I51" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>124</v>
       </c>
@@ -2626,8 +3898,17 @@
       <c r="F52" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G52" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I52" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>126</v>
       </c>
@@ -2646,8 +3927,17 @@
       <c r="F53" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G53" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I53" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>128</v>
       </c>
@@ -2666,8 +3956,17 @@
       <c r="F54" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G54" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="I54" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -2686,8 +3985,17 @@
       <c r="F55" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G55" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="I55" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>132</v>
       </c>
@@ -2706,8 +4014,17 @@
       <c r="F56" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G56" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="I56" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>133</v>
       </c>
@@ -2726,8 +4043,17 @@
       <c r="F57" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G57" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="I57" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>135</v>
       </c>
@@ -2746,8 +4072,17 @@
       <c r="F58" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G58" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="I58" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>137</v>
       </c>
@@ -2766,8 +4101,17 @@
       <c r="F59" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G59" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="I59" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>139</v>
       </c>
@@ -2786,8 +4130,17 @@
       <c r="F60" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G60" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I60" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
@@ -2806,8 +4159,17 @@
       <c r="F61" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G61" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="I61" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>144</v>
       </c>
@@ -2826,8 +4188,17 @@
       <c r="F62" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G62" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="I62" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>146</v>
       </c>
@@ -2846,8 +4217,17 @@
       <c r="F63" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G63" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I63" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>148</v>
       </c>
@@ -2866,8 +4246,17 @@
       <c r="F64" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G64" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I64" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>151</v>
       </c>
@@ -2886,8 +4275,17 @@
       <c r="F65" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G65" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="I65" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>153</v>
       </c>
@@ -2906,8 +4304,17 @@
       <c r="F66" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G66" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="I66" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>157</v>
       </c>
@@ -2926,8 +4333,17 @@
       <c r="F67" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G67" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I67" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>160</v>
       </c>
@@ -2946,8 +4362,17 @@
       <c r="F68" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G68" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I68" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>162</v>
       </c>
@@ -2966,8 +4391,17 @@
       <c r="F69" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G69" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I69" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>164</v>
       </c>
@@ -2986,8 +4420,17 @@
       <c r="F70" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G70" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="I70" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>166</v>
       </c>
@@ -3006,8 +4449,17 @@
       <c r="F71" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G71" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I71" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>168</v>
       </c>
@@ -3026,8 +4478,17 @@
       <c r="F72" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G72" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I72" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>170</v>
       </c>
@@ -3046,8 +4507,17 @@
       <c r="F73" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G73" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="I73" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>172</v>
       </c>
@@ -3066,8 +4536,17 @@
       <c r="F74" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G74" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="I74" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>174</v>
       </c>
@@ -3086,8 +4565,17 @@
       <c r="F75" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G75" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="I75" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>175</v>
       </c>
@@ -3106,8 +4594,17 @@
       <c r="F76" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G76" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="I76" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>177</v>
       </c>
@@ -3126,8 +4623,17 @@
       <c r="F77" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G77" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="I77" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>179</v>
       </c>
@@ -3146,8 +4652,17 @@
       <c r="F78" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G78" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="I78" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>180</v>
       </c>
@@ -3166,8 +4681,17 @@
       <c r="F79" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G79" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="I79" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>182</v>
       </c>
@@ -3186,8 +4710,17 @@
       <c r="F80" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G80" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="I80" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>184</v>
       </c>
@@ -3206,8 +4739,17 @@
       <c r="F81" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G81" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="I81" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>186</v>
       </c>
@@ -3226,8 +4768,17 @@
       <c r="F82" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G82" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I82" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>188</v>
       </c>
@@ -3246,8 +4797,17 @@
       <c r="F83" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G83" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="I83" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>190</v>
       </c>
@@ -3266,8 +4826,17 @@
       <c r="F84" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G84" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="I84" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>193</v>
       </c>
@@ -3286,8 +4855,17 @@
       <c r="F85" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G85" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I85" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>195</v>
       </c>
@@ -3306,8 +4884,17 @@
       <c r="F86" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G86" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I86" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>197</v>
       </c>
@@ -3326,8 +4913,17 @@
       <c r="F87" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G87" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I87" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>200</v>
       </c>
@@ -3346,8 +4942,17 @@
       <c r="F88" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G88" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I88" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>202</v>
       </c>
@@ -3366,8 +4971,17 @@
       <c r="F89" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G89" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I89" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>204</v>
       </c>
@@ -3386,8 +5000,17 @@
       <c r="F90" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G90" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I90" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>63</v>
       </c>
@@ -3406,8 +5029,17 @@
       <c r="F91" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G91" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="I91" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>22</v>
       </c>
@@ -3426,8 +5058,17 @@
       <c r="F92" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G92" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="I92" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>208</v>
       </c>
@@ -3446,8 +5087,17 @@
       <c r="F93" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G93" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="I93" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
@@ -3466,8 +5116,17 @@
       <c r="F94" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G94" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I94" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>212</v>
       </c>
@@ -3486,8 +5145,17 @@
       <c r="F95" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G95" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I95" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>214</v>
       </c>
@@ -3506,8 +5174,17 @@
       <c r="F96" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G96" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="I96" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>216</v>
       </c>
@@ -3526,8 +5203,17 @@
       <c r="F97" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G97" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I97" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>218</v>
       </c>
@@ -3546,8 +5232,17 @@
       <c r="F98" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G98" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="I98" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>220</v>
       </c>
@@ -3566,8 +5261,17 @@
       <c r="F99" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G99" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="I99" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>221</v>
       </c>
@@ -3586,8 +5290,17 @@
       <c r="F100" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G100" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="I100" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>223</v>
       </c>
@@ -3606,8 +5319,17 @@
       <c r="F101" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G101" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I101" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>225</v>
       </c>
@@ -3626,8 +5348,17 @@
       <c r="F102" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G102" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="I102" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>227</v>
       </c>
@@ -3646,8 +5377,17 @@
       <c r="F103" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G103" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="I103" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>229</v>
       </c>
@@ -3666,8 +5406,17 @@
       <c r="F104" s="1" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G104" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="I104" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>231</v>
       </c>
@@ -3686,8 +5435,17 @@
       <c r="F105" s="1" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G105" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I105" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>234</v>
       </c>
@@ -3706,8 +5464,17 @@
       <c r="F106" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G106" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I106" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>236</v>
       </c>
@@ -3726,8 +5493,17 @@
       <c r="F107" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G107" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I107" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>238</v>
       </c>
@@ -3746,8 +5522,17 @@
       <c r="F108" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G108" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I108" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>241</v>
       </c>
@@ -3766,8 +5551,17 @@
       <c r="F109" s="1" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G109" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="I109" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>244</v>
       </c>
@@ -3786,8 +5580,17 @@
       <c r="F110" s="1" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G110" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="I110" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>248</v>
       </c>
@@ -3806,8 +5609,17 @@
       <c r="F111" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G111" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I111" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>250</v>
       </c>
@@ -3826,8 +5638,17 @@
       <c r="F112" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G112" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I112" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>252</v>
       </c>
@@ -3846,8 +5667,17 @@
       <c r="F113" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G113" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="I113" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>254</v>
       </c>
@@ -3866,8 +5696,17 @@
       <c r="F114" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G114" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I114" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>257</v>
       </c>
@@ -3886,8 +5725,17 @@
       <c r="F115" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G115" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I115" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>259</v>
       </c>
@@ -3906,8 +5754,17 @@
       <c r="F116" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G116" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="I116" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>261</v>
       </c>
@@ -3926,8 +5783,17 @@
       <c r="F117" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G117" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I117" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>263</v>
       </c>
@@ -3946,8 +5812,17 @@
       <c r="F118" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G118" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="I118" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>266</v>
       </c>
@@ -3966,8 +5841,17 @@
       <c r="F119" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G119" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I119" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>268</v>
       </c>
@@ -3986,8 +5870,17 @@
       <c r="F120" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G120" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I120" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>270</v>
       </c>
@@ -4006,8 +5899,17 @@
       <c r="F121" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G121" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I121" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>272</v>
       </c>
@@ -4026,8 +5928,17 @@
       <c r="F122" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G122" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="I122" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>274</v>
       </c>
@@ -4046,8 +5957,17 @@
       <c r="F123" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G123" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I123" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>276</v>
       </c>
@@ -4066,8 +5986,17 @@
       <c r="F124" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G124" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I124" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>278</v>
       </c>
@@ -4086,8 +6015,17 @@
       <c r="F125" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G125" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I125" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>281</v>
       </c>
@@ -4106,8 +6044,17 @@
       <c r="F126" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G126" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I126" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>283</v>
       </c>
@@ -4126,8 +6073,17 @@
       <c r="F127" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G127" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I127" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>286</v>
       </c>
@@ -4146,8 +6102,17 @@
       <c r="F128" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G128" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I128" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>288</v>
       </c>
@@ -4166,8 +6131,17 @@
       <c r="F129" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G129" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>290</v>
       </c>
@@ -4186,8 +6160,17 @@
       <c r="F130" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G130" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>292</v>
       </c>
@@ -4206,8 +6189,17 @@
       <c r="F131" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G131" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>294</v>
       </c>
@@ -4226,8 +6218,17 @@
       <c r="F132" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G132" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>296</v>
       </c>
@@ -4246,8 +6247,17 @@
       <c r="F133" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G133" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I133" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>298</v>
       </c>
@@ -4266,8 +6276,17 @@
       <c r="F134" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G134" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I134" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>300</v>
       </c>
@@ -4286,8 +6305,17 @@
       <c r="F135" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G135" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I135" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>302</v>
       </c>
@@ -4306,8 +6334,17 @@
       <c r="F136" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G136" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I136" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>304</v>
       </c>
@@ -4326,8 +6363,17 @@
       <c r="F137" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G137" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I137" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>306</v>
       </c>
@@ -4346,8 +6392,17 @@
       <c r="F138" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G138" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I138" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>308</v>
       </c>
@@ -4366,8 +6421,17 @@
       <c r="F139" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G139" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I139" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>310</v>
       </c>
@@ -4386,8 +6450,17 @@
       <c r="F140" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G140" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I140" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>312</v>
       </c>
@@ -4406,8 +6479,17 @@
       <c r="F141" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G141" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="I141" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>79</v>
       </c>
@@ -4426,8 +6508,17 @@
       <c r="F142" s="1" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G142" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="I142" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>316</v>
       </c>
@@ -4446,8 +6537,17 @@
       <c r="F143" s="1" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G143" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="I143" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>318</v>
       </c>
@@ -4466,8 +6566,17 @@
       <c r="F144" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G144" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="I144" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>320</v>
       </c>
@@ -4486,8 +6595,17 @@
       <c r="F145" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G145" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="I145" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>322</v>
       </c>
@@ -4506,8 +6624,17 @@
       <c r="F146" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G146" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="I146" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>324</v>
       </c>
@@ -4526,8 +6653,17 @@
       <c r="F147" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G147" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="I147" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>326</v>
       </c>
@@ -4546,8 +6682,17 @@
       <c r="F148" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G148" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I148" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>328</v>
       </c>
@@ -4566,8 +6711,17 @@
       <c r="F149" s="1" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G149" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I149" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>331</v>
       </c>
@@ -4586,8 +6740,17 @@
       <c r="F150" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G150" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I150" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>333</v>
       </c>
@@ -4606,8 +6769,17 @@
       <c r="F151" s="1" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G151" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I151" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>336</v>
       </c>
@@ -4626,8 +6798,17 @@
       <c r="F152" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G152" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I152" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>338</v>
       </c>
@@ -4646,8 +6827,17 @@
       <c r="F153" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G153" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="I153" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>340</v>
       </c>
@@ -4666,8 +6856,17 @@
       <c r="F154" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G154" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="I154" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>342</v>
       </c>
@@ -4686,8 +6885,17 @@
       <c r="F155" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G155" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="I155" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>51</v>
       </c>
@@ -4706,8 +6914,17 @@
       <c r="F156" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G156" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="I156" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>345</v>
       </c>
@@ -4726,8 +6943,17 @@
       <c r="F157" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G157" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="I157" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>348</v>
       </c>
@@ -4746,8 +6972,17 @@
       <c r="F158" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G158" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="I158" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>350</v>
       </c>
@@ -4766,8 +7001,17 @@
       <c r="F159" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G159" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="I159" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>353</v>
       </c>
@@ -4786,8 +7030,17 @@
       <c r="F160" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G160" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I160" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>355</v>
       </c>
@@ -4806,8 +7059,17 @@
       <c r="F161" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G161" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I161" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>357</v>
       </c>
@@ -4826,8 +7088,17 @@
       <c r="F162" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G162" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I162" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>359</v>
       </c>
@@ -4846,8 +7117,17 @@
       <c r="F163" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G163" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="I163" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>361</v>
       </c>
@@ -4866,8 +7146,17 @@
       <c r="F164" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G164" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="I164" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>363</v>
       </c>
@@ -4886,8 +7175,17 @@
       <c r="F165" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G165" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="I165" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>365</v>
       </c>
@@ -4906,8 +7204,17 @@
       <c r="F166" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G166" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="I166" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>367</v>
       </c>
@@ -4926,8 +7233,17 @@
       <c r="F167" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G167" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I167" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>369</v>
       </c>
@@ -4946,8 +7262,17 @@
       <c r="F168" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G168" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="I168" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>371</v>
       </c>
@@ -4966,8 +7291,17 @@
       <c r="F169" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G169" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="I169" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>373</v>
       </c>
@@ -4986,8 +7320,17 @@
       <c r="F170" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G170" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="I170" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>375</v>
       </c>
@@ -5006,8 +7349,17 @@
       <c r="F171" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G171" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="I171" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>377</v>
       </c>
@@ -5026,8 +7378,17 @@
       <c r="F172" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G172" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="I172" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>379</v>
       </c>
@@ -5046,8 +7407,17 @@
       <c r="F173" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G173" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="I173" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>381</v>
       </c>
@@ -5066,8 +7436,17 @@
       <c r="F174" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G174" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="I174" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>383</v>
       </c>
@@ -5085,6 +7464,15 @@
       </c>
       <c r="F175" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="I175" s="1">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Faculties/Law/Undergrad Modules Law.xlsx
+++ b/Faculties/Law/Undergrad Modules Law.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Law/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{EA53A12A-4D1C-42A1-A583-74F28C4B0ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71DC0CB9-CCB9-4734-8571-08AFADF79716}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{EA53A12A-4D1C-42A1-A583-74F28C4B0ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EA8C5E6-29F1-4013-B247-96C1C2558310}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="9984" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="992">
   <si>
     <t>Module Code</t>
   </si>
@@ -2047,6 +2047,960 @@
   </si>
   <si>
     <t>Compensation for occupational injuries/diseases; Unemployment Insurance; workplace health/safety; pensions; retirement funds; and social assistance</t>
+  </si>
+  <si>
+    <t>ADL711</t>
+  </si>
+  <si>
+    <t>Administrative Law 711</t>
+  </si>
+  <si>
+    <t>PGDip Public Law 7711</t>
+  </si>
+  <si>
+    <t>Discuss the main principles of administrative law; evaluate administrative powers and jurisdiction; analyze administrative action as per PAJA; and apply requirements for valid administrative actions to practical scenarios.</t>
+  </si>
+  <si>
+    <t>Foundations of administrative law; PAJA; powers and jurisdiction; action and control; valid administrative action requirements; standing and procedure; and remedies.</t>
+  </si>
+  <si>
+    <t>CLL713</t>
+  </si>
+  <si>
+    <t>Constitutional Law 713</t>
+  </si>
+  <si>
+    <t>Articulate values underlying the Constitution and evaluate its principles; interpret the Constitution in hypothetical scenarios; evaluate government structure and powers; and compare the SA constitution within international contexts.</t>
+  </si>
+  <si>
+    <t>Constitutional values and principles; constitutional history; constitutional interpretation; Bill of Rights; federalism; and the separation of powers.</t>
+  </si>
+  <si>
+    <t>CRJ711</t>
+  </si>
+  <si>
+    <t>Criminal Justice Systems and Human Rights in Africa 711</t>
+  </si>
+  <si>
+    <t>Critically evaluate the intersection between criminal justice systems and human rights in Africa, specifically focusing on vulnerable groups and unusual circumstances (e.g., states of emergency and disaster).</t>
+  </si>
+  <si>
+    <t>Criminal justice systems and human rights in Africa.</t>
+  </si>
+  <si>
+    <t>ENL711</t>
+  </si>
+  <si>
+    <t>Advanced Environmental Law 711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGDip Environmental Law and Management 7712 </t>
+  </si>
+  <si>
+    <t>Identify and critically discuss the main rules, procedures, and principles of South African Environmental Law.</t>
+  </si>
+  <si>
+    <t>South African Environmental Law.</t>
+  </si>
+  <si>
+    <t>ENL712</t>
+  </si>
+  <si>
+    <t>Environmental Governance 712</t>
+  </si>
+  <si>
+    <t>Critically discuss the nature, scope, and function of environmental governance; analyze rules, theories, and foundations in SA; and evaluate the Constitution and enabling legal framework.</t>
+  </si>
+  <si>
+    <t>Environmental governance in South Africa.</t>
+  </si>
+  <si>
+    <t>ENL713</t>
+  </si>
+  <si>
+    <t>Environmental Administrative Law 713</t>
+  </si>
+  <si>
+    <t>Critically discuss and apply Administrative Law principles to Environmental Law; evaluate administrative powers/jurisdiction; and analyze just administrative action.</t>
+  </si>
+  <si>
+    <t>Foundations and rules of Administrative Law in environmental context; Constitution (environmental right, access to info); requirements for valid action; and remedies.</t>
+  </si>
+  <si>
+    <t>ENL714</t>
+  </si>
+  <si>
+    <t>Environmental Management 714</t>
+  </si>
+  <si>
+    <t>Critically discuss principles of environmental management and their link to governance; discuss integrated management; and evaluate the rationale behind Environmental Impact Assessments.</t>
+  </si>
+  <si>
+    <t>Environmental Impact Assessment and general environmental management.</t>
+  </si>
+  <si>
+    <t>FTL711</t>
+  </si>
+  <si>
+    <t>Concepts in Fintech Law 711</t>
+  </si>
+  <si>
+    <t>PGDip Fintech Law and Regulation 7702</t>
+  </si>
+  <si>
+    <t>Consult the Centre for African Fintech, Innovation and Law (CAFIL) for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>Introduction to concepts in Fintech Law.</t>
+  </si>
+  <si>
+    <t>FTL712</t>
+  </si>
+  <si>
+    <t>Banking and Financial Regulation 712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGDip Fintech Law and Regulation 7702 </t>
+  </si>
+  <si>
+    <t>Banking system; virtual currencies, cryptocurrencies, and central bank digital currencies; and mobile money/financial inclusion.</t>
+  </si>
+  <si>
+    <t>FTL713</t>
+  </si>
+  <si>
+    <t>Fintech Payment Regulation 713</t>
+  </si>
+  <si>
+    <t>Distinguish between payment systems regulation and oversight; and critically discuss and evaluate the meaning and legal nature of fintech payments.</t>
+  </si>
+  <si>
+    <t>Fintech payment regulation.</t>
+  </si>
+  <si>
+    <t>FTL714</t>
+  </si>
+  <si>
+    <t>Trade-offs in Fintech Regulation 714</t>
+  </si>
+  <si>
+    <t>Critically discuss the meaning and nature of financial inclusion and integrity; and analyze their relationship with Fintech.</t>
+  </si>
+  <si>
+    <t>Trade-offs in Fintech regulation.</t>
+  </si>
+  <si>
+    <t>MLG714</t>
+  </si>
+  <si>
+    <t>Multi-level Governance 714</t>
+  </si>
+  <si>
+    <t>Evaluate the constitution and enabling framework for multi-level government in SA; locate the system within international debates; and compare provincial government finance sources.</t>
+  </si>
+  <si>
+    <t>Power distribution between national, provincial, and local government; constitutional framework; multi-level finance; and intergovernmental relations.</t>
+  </si>
+  <si>
+    <t>LGL712</t>
+  </si>
+  <si>
+    <t>Local Government 712</t>
+  </si>
+  <si>
+    <t>Articulate the constitution and enabling framework for local government in SA; identify strategies to integrate ethics and good governance; and locate the system within international debates.</t>
+  </si>
+  <si>
+    <t>Local government.</t>
+  </si>
+  <si>
+    <t>PGL711</t>
+  </si>
+  <si>
+    <t>Labour Law in Context 711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGDip Labour Law 7701 </t>
+  </si>
+  <si>
+    <t>Critically analyze the elements of collective bargaining (including industrial action); demonstrate ability to engage with practical requirements; and apply statutory provisions for business transfers.</t>
+  </si>
+  <si>
+    <t>Historical development of SA labour law; contract principles; the constitutional framework (LRA, BCEA, EEA); legal interpretation; and collective bargaining.</t>
+  </si>
+  <si>
+    <t>PGL712</t>
+  </si>
+  <si>
+    <t>The Right to Fair Labour Practices 712</t>
+  </si>
+  <si>
+    <t>Analyze concepts relevant to dismissal and unfair labour practices; demonstrate knowledge of constitutional/international rights; explain the role of common law; and apply SA labour legislation.</t>
+  </si>
+  <si>
+    <t>The right to fair labour practices.</t>
+  </si>
+  <si>
+    <t>PGL721</t>
+  </si>
+  <si>
+    <t>Labour Dispute Resolution 721</t>
+  </si>
+  <si>
+    <t>Consult the Mercantile and Labour Law Department for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>Labour dispute resolution.</t>
+  </si>
+  <si>
+    <t>PGL722</t>
+  </si>
+  <si>
+    <t>Advanced Dispute Resolution Procedure 722</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of ethical issues in conciliation and arbitration; explain and apply conciliation process elements; and demonstrate ability to conduct conciliation.</t>
+  </si>
+  <si>
+    <t>Conciliation; con-arb; conducting arbitration; representation; duties and powers; evidence admissibility; and arbitration awards (variation, rescission, and review).</t>
+  </si>
+  <si>
+    <t>PUB711</t>
+  </si>
+  <si>
+    <t>Detention and Oversight 711</t>
+  </si>
+  <si>
+    <t>Consult the Dullah Omar Institute for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>Detention and oversight, with specific reference to vulnerable groups and emergency/disaster situations.</t>
+  </si>
+  <si>
+    <t>TXL711</t>
+  </si>
+  <si>
+    <t>Advanced Income Tax Law 711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGDip Tax Law 7721 </t>
+  </si>
+  <si>
+    <t>Critically analyze "gross income" and constituent elements; understand residence and "place of effective management"; interpret source rules; and solve problems in factual scenarios.</t>
+  </si>
+  <si>
+    <t>Interpretation of fiscal statutes; Constitution impact; gross income (resident/non-resident); partnerships; revenue vs capital; and taxation of cryptocurrency.</t>
+  </si>
+  <si>
+    <t>TXL712</t>
+  </si>
+  <si>
+    <t>International Tax Law 712</t>
+  </si>
+  <si>
+    <t>Critically analyze fundamental concepts in international taxation; understand OECD model conventions; interpret double tax agreements; and evaluate international transactions.</t>
+  </si>
+  <si>
+    <t>International tax law.</t>
+  </si>
+  <si>
+    <t>TXL713</t>
+  </si>
+  <si>
+    <t>Tax Administration 713</t>
+  </si>
+  <si>
+    <t>Analyze legal concepts under the TAA, PAJA, and the Constitution; explain taxpayer rights (privacy, property, access); and interpret rules governing appeals and objections.</t>
+  </si>
+  <si>
+    <t>Inter-relationship between TAA, PAJA, and the Constitution; taxpayer rights to just administrative action and court access; and appeal/objection rules.</t>
+  </si>
+  <si>
+    <t>TXL714</t>
+  </si>
+  <si>
+    <t>Estate Planning Law 714</t>
+  </si>
+  <si>
+    <t>Critically understand the concept of estate duty and its SA operation; understand the meaning of an "estate"; and explain components relevant to determining dutiable amounts.</t>
+  </si>
+  <si>
+    <t>Estate planning law.</t>
+  </si>
+  <si>
+    <t>ACL811</t>
+  </si>
+  <si>
+    <t>Anti-Corruption Law 811</t>
+  </si>
+  <si>
+    <t>LLM 7801, LLM 7821, LLM 7822</t>
+  </si>
+  <si>
+    <t>Comprehend national/international dimensions of corruption; understand corruption as a barrier to development and human rights; and recognize/assess obstacles to anti-corruption practices.</t>
+  </si>
+  <si>
+    <t>Corruption meaning and extent; forms; evolution of law; SA anti-corruption statutes/cases; prevention and prosecution; collaboration; and asset recovery.</t>
+  </si>
+  <si>
+    <t>AML811</t>
+  </si>
+  <si>
+    <t>Anti-Money Laundering Law 811</t>
+  </si>
+  <si>
+    <t>Consult the Criminal Justice and Procedure Department for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>Anti-money laundering law transnationally.</t>
+  </si>
+  <si>
+    <t>CCL811</t>
+  </si>
+  <si>
+    <t>Comparative Constitutional Law 811</t>
+  </si>
+  <si>
+    <t>LLM 7801, LLM 7821, LLM 7822, MPhil 7871, MPhil 7860, MPhil 7861</t>
+  </si>
+  <si>
+    <t>Apply comparative constitutional law methodology; and critically analyze constitutions regarding organizing government, rights models, constitutional review, and reform mechanisms.</t>
+  </si>
+  <si>
+    <t>Comparative law methodologies; principles; constitution making; systems/forms of government; judicial appointment; emergency powers; and review models.</t>
+  </si>
+  <si>
+    <t>CDS811</t>
+  </si>
+  <si>
+    <t>Constitutional Design in Divided Societies 811</t>
+  </si>
+  <si>
+    <t>Evaluate how a divided society's constitution can design state institutions to manage communities; demonstrate knowledge of constitutional choices for multi-ethnic states; and analyze options for polarized societies.</t>
+  </si>
+  <si>
+    <t>Challenges of divided societies; Bill of Rights response; constitutionalism; federalism; territorial pluralism; electoral systems; and language policy.</t>
+  </si>
+  <si>
+    <t>CIN800</t>
+  </si>
+  <si>
+    <t>Constitutional Rights Interpretation 800</t>
+  </si>
+  <si>
+    <t>Analyze challenges facing rights interpretation in young democracies; understand hermeneutic/political factors; and identify and solve problems relating to specific constitutional rights.</t>
+  </si>
+  <si>
+    <t>Theories of interpretation; doctrines (separation of powers, popular constitutionalism); hermeneutic factors (text, values); and alternative theories (textualism, deconstruction).</t>
+  </si>
+  <si>
+    <t>CIN811</t>
+  </si>
+  <si>
+    <t>Constitutional Law, Politics and Theory 811</t>
+  </si>
+  <si>
+    <t>Critically evaluate the concepts and ideas central to modern constitutions; and provide in-depth research analysis of covered topics.</t>
+  </si>
+  <si>
+    <t>The concept of the ‘political’ and the ‘constitution’; sovereignty; constituent power; democracy; and contemporary problems (e.g., right to the city, decolonial perspectives).</t>
+  </si>
+  <si>
+    <t>CLL811</t>
+  </si>
+  <si>
+    <t>Constitutional Law Practice 811</t>
+  </si>
+  <si>
+    <t>Acquire an understanding of how constitutional law is applied in practice; provide legal advice/opinions on interpretation in practical situations; and solve problems using creative thinking.</t>
+  </si>
+  <si>
+    <t>Practical research in constitutional law; internship experience at an institution of democracy; and praxis of application.</t>
+  </si>
+  <si>
+    <t>CLL812</t>
+  </si>
+  <si>
+    <t>Constitutional Rights and Criminal Justice 812</t>
+  </si>
+  <si>
+    <t>Analyze fundamental concepts and principles of constitutional interpretation in criminal justice; demonstrate knowledge of the Bill of Rights; and evaluate case law.</t>
+  </si>
+  <si>
+    <t>Bill of Rights examining: privacy and police powers (search/seizure); arrest and force; detainee rights (legal services); bail; and fair trial.</t>
+  </si>
+  <si>
+    <t>CLL814</t>
+  </si>
+  <si>
+    <t>Multi-level Governance 814</t>
+  </si>
+  <si>
+    <t>Analyze fundamental legal concepts, theories, and practices of intergovernmental relations in SA; and identify and solve problems regarding dispersal of powers and supervisory reach.</t>
+  </si>
+  <si>
+    <t>Multi-level governance.</t>
+  </si>
+  <si>
+    <t>CLL815</t>
+  </si>
+  <si>
+    <t>Gender Equality and Women’s Rights 815</t>
+  </si>
+  <si>
+    <t>Critically evaluate, apply, and reflect on concepts and theories relating to substantive gender equality and women’s rights; and conduct analysis from a gender perspective.</t>
+  </si>
+  <si>
+    <t>Gender equality and women’s rights.</t>
+  </si>
+  <si>
+    <t>CLL816</t>
+  </si>
+  <si>
+    <t>Legal Pluralism 816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM 7801, LLM 7821, LLM 7822, MPhil 7871, MPhil 7860, MPhil 7861, LLM 7801, LLM 7821, LLM 7822 LPFL </t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of pluralism theories; challenge mainstream conceptualizations of customary law; explain pluralism as a product of legal history; and critique the indigenous-state law relationship.</t>
+  </si>
+  <si>
+    <t>Historical context; impact of colonial rule; major theories vs cultural relativism; customary law critique; dialogue areas between state and indigenous laws; and decolonization.</t>
+  </si>
+  <si>
+    <t>CLL817</t>
+  </si>
+  <si>
+    <t>Children’s Rights 817</t>
+  </si>
+  <si>
+    <t>Children’s rights.</t>
+  </si>
+  <si>
+    <t>CLL818</t>
+  </si>
+  <si>
+    <t>Climate Law and Governance 818</t>
+  </si>
+  <si>
+    <t>IEL812</t>
+  </si>
+  <si>
+    <t>Consult the Global Environmental Law Centre for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>Climate change law and relevant governance; sectoral legislation; principles; international/SA actors; climate justice; and damages/liability.</t>
+  </si>
+  <si>
+    <t>CLL819</t>
+  </si>
+  <si>
+    <t>Constitutional Law and Nature 819</t>
+  </si>
+  <si>
+    <t>Evaluate law for protecting nature and non-human animals; analyze taxonomy of environmental constitutionalism; and understand Earth Jurisprudence/non-anthropocentric approaches.</t>
+  </si>
+  <si>
+    <t>Governance scope for environment/nature; right holders; substantive/procedural rights; and concepts (Anthropocentrism, Rule of Law, Public Trust, Rights of Nature).</t>
+  </si>
+  <si>
+    <t>CLL821</t>
+  </si>
+  <si>
+    <t>Animal Law and Rights 821</t>
+  </si>
+  <si>
+    <t>Critically evaluate the philosophical, ethical, scientific, and legal foundations of the protection of animals in South Africa and globally.</t>
+  </si>
+  <si>
+    <t>Current legal system deficiencies; core concepts (welfare, legal personhood, sentience, speciesism); and animal rights in the courts.</t>
+  </si>
+  <si>
+    <t>COR811</t>
+  </si>
+  <si>
+    <t>Corporate Governance and Remedies 811</t>
+  </si>
+  <si>
+    <t>Analyze fundamental concepts and principles of corporate governance; examine main role players; evaluate SA regulation vs international practice; and identify shortcomings/solutions.</t>
+  </si>
+  <si>
+    <t>Theories of governance; King Reports (I-IV); role players; comparative studies (CSR, Ethical Leadership, Criminal Liability); and corporate law remedies.</t>
+  </si>
+  <si>
+    <t>COR812</t>
+  </si>
+  <si>
+    <t>Corporate Financial Regulation 812</t>
+  </si>
+  <si>
+    <t>Conceptualize Approach to financial regulation (Companies Act 2008); interpret decision-making principles for corporate finance; and explain rules for market abuse prevention.</t>
+  </si>
+  <si>
+    <t>SA/international principles; funding sources (equity); capital regulation (solvency/liquidity); distributions; and policy objectives of securities/financial markets.</t>
+  </si>
+  <si>
+    <t>COR813</t>
+  </si>
+  <si>
+    <t>Corporate Insolvency Law 813</t>
+  </si>
+  <si>
+    <t>Analyze options when a company enters the zone of insolvency; explain business rescue regulation and practice; and interpret relevant case law and statutes.</t>
+  </si>
+  <si>
+    <t>Corporate solvency principles; restructuring; business rescue framework (Practitioner powers, plan, termination); liquidations; and cross-border issues.</t>
+  </si>
+  <si>
+    <t>CPL811</t>
+  </si>
+  <si>
+    <t>Constitutional Property Law 811</t>
+  </si>
+  <si>
+    <t>Demonstrate specialist knowledge of "property" (section 25); interpret regulatory control (planning, mining, neighbor law); and design alternative land reform strategies.</t>
+  </si>
+  <si>
+    <t>SA Bill of Rights (property); legal framework for regulatory control; methodological approaches; and the property relationship with other constitutional rights.</t>
+  </si>
+  <si>
+    <t>CPL812</t>
+  </si>
+  <si>
+    <t>Land Reform and Housing Law 812</t>
+  </si>
+  <si>
+    <t>Consult the Private Law Department for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>Land reform and housing law.</t>
+  </si>
+  <si>
+    <t>CPT811</t>
+  </si>
+  <si>
+    <t>Competition Law and Regulation 811</t>
+  </si>
+  <si>
+    <t>Demonstrate specialist knowledge of competition theoretical underpinnings; explain competition economics; apply rules to practical scenarios; and analyze social justice relations.</t>
+  </si>
+  <si>
+    <t>Harvard/Chicago schools; economics/structures; horizontal/vertical practices; mergers; abuse of dominance; jurisdictions; and relations with IP, information, and labour law.</t>
+  </si>
+  <si>
+    <t>CPT812</t>
+  </si>
+  <si>
+    <t>Competition Law and Work 812</t>
+  </si>
+  <si>
+    <t>Identify and critically analyze the link between competition and labour law; analyze effects of employer monopsony power; and conceptualize "platform work" impact.</t>
+  </si>
+  <si>
+    <t>General principles/economics; market structures (monopsonies); defining workers; labour rights; Competition Act scope; and transformation/digitisation.</t>
+  </si>
+  <si>
+    <t>CPT813</t>
+  </si>
+  <si>
+    <t>Mergers and Acquisitions 813</t>
+  </si>
+  <si>
+    <t>Conceptualize amalgamations/mergers and underpinning policies; interpret the legal framework (Companies Act 2008, Competition Act 1998); and explain takeover regulation.</t>
+  </si>
+  <si>
+    <t>Fundamental transactions; merger structures and effect; statutory merger procedures (Companies/Competition Acts); stakeholder protection; and the Takeover Regulation Panel.</t>
+  </si>
+  <si>
+    <t>CPT814</t>
+  </si>
+  <si>
+    <t>Competition and Information Law 814</t>
+  </si>
+  <si>
+    <t>Understand dynamic functions of a modern economy; conceptualize key areas of information law in the digital age; and critically evaluate competition in the digital economy.</t>
+  </si>
+  <si>
+    <t>Online consumer protection; privacy; computer crime; trade in digital services; AI; digital taxation; and technological approaches to enforcement in digital markets.</t>
+  </si>
+  <si>
+    <t>DLP812</t>
+  </si>
+  <si>
+    <t>Disability Law and the Workplace 812</t>
+  </si>
+  <si>
+    <t>Demonstrate a specialist knowledge of the international legal framework relating to disability and the workplace.</t>
+  </si>
+  <si>
+    <t>Disability law and the workplace.</t>
+  </si>
+  <si>
+    <t>DPR811</t>
+  </si>
+  <si>
+    <t>Dispute Resolution 811</t>
+  </si>
+  <si>
+    <t>Negotiation, mediation, and arbitration processes; SA Truth and Reconciliation Commission; and restorative justice.</t>
+  </si>
+  <si>
+    <t>ESP811</t>
+  </si>
+  <si>
+    <t>The Extension of Social Protection 811</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of, and ability to analyse, fundamental legal concepts of social protection.</t>
+  </si>
+  <si>
+    <t>The extension of social protection.</t>
+  </si>
+  <si>
+    <t>FAM811</t>
+  </si>
+  <si>
+    <t>International Family Law 811</t>
+  </si>
+  <si>
+    <t>Consult the Centre for Legal Integration in Africa (CLIA) for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>International family law.</t>
+  </si>
+  <si>
+    <t>IAL812</t>
+  </si>
+  <si>
+    <t>International Anti-Corruption Law 812</t>
+  </si>
+  <si>
+    <t>Appreciate the significance of corruption as an international crisis; understand it as a barrier to socio-economic development; and recognize obstacles to anti-corruption practices.</t>
+  </si>
+  <si>
+    <t>International anti-corruption law.</t>
+  </si>
+  <si>
+    <t>IEL811</t>
+  </si>
+  <si>
+    <t>International Environmental Law 811</t>
+  </si>
+  <si>
+    <t>ENV431/equiv</t>
+  </si>
+  <si>
+    <t>Evaluate what constitutes the "environment" internationally; and understand the application of international/regional policies and legal norms in SA domestic law.</t>
+  </si>
+  <si>
+    <t>IEL and SADC law pertaining to environment (SA perspective); Biodiversity; Sea/Wildlife law; Climate Change; and trade/development.</t>
+  </si>
+  <si>
+    <t>Advanced Environmental Law 812</t>
+  </si>
+  <si>
+    <t>IEL811 (pref)</t>
+  </si>
+  <si>
+    <t>Critically evaluate the "environment"; identify ethical duties; identify complex environmentally related matters; and apply specialist knowledge to address/solve them.</t>
+  </si>
+  <si>
+    <t>Environment law scope; international/human rights dimensions; administration; implementation/enforcement; and natural/cultural resource utilization.</t>
+  </si>
+  <si>
+    <t>IHR811</t>
+  </si>
+  <si>
+    <t>International Criminal Law 811</t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of international crimes; identify principles from sources to solve cases; evaluate ICC enforcement; and assess African reform/decolonisation proposals.</t>
+  </si>
+  <si>
+    <t>International criminal law.</t>
+  </si>
+  <si>
+    <t>IHR812</t>
+  </si>
+  <si>
+    <t>Transitional Justice 812</t>
+  </si>
+  <si>
+    <t>Demonstrate knowledge of meaning/origin/debates; critically analyze AU approach within decolonized context; and conduct research for transitional justice scenarios.</t>
+  </si>
+  <si>
+    <t>Research/writing; theories (amnesty, truth, commissions); international law (Human rights/humanitarian); context studies (SA, Rwanda, DRC, etc.).</t>
+  </si>
+  <si>
+    <t>IHR813</t>
+  </si>
+  <si>
+    <t>Comparative Regional Integration &amp; Dev. 813</t>
+  </si>
+  <si>
+    <t>Comparative regional integration; trade; and human rights protection.</t>
+  </si>
+  <si>
+    <t>IHR814</t>
+  </si>
+  <si>
+    <t>Int. Protection of Human Rights Law 814</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of fundamental concepts/principles/theories; and apply research methods and strategies to theoretical and applied situations.</t>
+  </si>
+  <si>
+    <t>Introduction to African, European, Inter-American, Asian, and Arab systems for human rights protection.</t>
+  </si>
+  <si>
+    <t>IHR815</t>
+  </si>
+  <si>
+    <t>International Humanitarian Law 815</t>
+  </si>
+  <si>
+    <t>Consult the African Centre for Transnational Criminal Justice for detailed outcomes.</t>
+  </si>
+  <si>
+    <t>International humanitarian law.</t>
+  </si>
+  <si>
+    <t>IHR816</t>
+  </si>
+  <si>
+    <t>Global Human Rights Issues 816</t>
+  </si>
+  <si>
+    <t>Critically analyze contemporary human rights issues; evaluate monitoring limits and politicization; and analyze links between rights, development, and poverty.</t>
+  </si>
+  <si>
+    <t>Global human rights issues.</t>
+  </si>
+  <si>
+    <t>IPL831</t>
+  </si>
+  <si>
+    <t>Intellectual Property Law 831</t>
+  </si>
+  <si>
+    <t>Critically discuss fundamental legal theories, concepts, and principles of intellectual property.</t>
+  </si>
+  <si>
+    <t>Intellectual property law.</t>
+  </si>
+  <si>
+    <t>ITB811</t>
+  </si>
+  <si>
+    <t>International Trade 811</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of concepts and principles; and apply methods and strategies involved in legal research and problem solving.</t>
+  </si>
+  <si>
+    <t>International trade law practices; international economic/trade dispute settlement (arbitration).</t>
+  </si>
+  <si>
+    <t>ITB812</t>
+  </si>
+  <si>
+    <t>International Business &amp; Regional Trade Law 812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM 7801, LLM 7821, LLM 7822 7811 </t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of concepts, principles, theories, and their relationship to international business practices.</t>
+  </si>
+  <si>
+    <t>Sales, finance, and competition forms; arbitration; environmental/social considerations; EU Law; AGOA, SADC, AU roles; and African trade negotiation roles.</t>
+  </si>
+  <si>
+    <t>ITB813</t>
+  </si>
+  <si>
+    <t>International Economic &amp; Investment Law 813</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of, and ability to analyse, fundamental legal concepts and principles of investment law.</t>
+  </si>
+  <si>
+    <t>Public/private international law; state responsibility; treaties; global institutes (UNCTAD, AfDB, IMF); WTO regulation; IP (TRIPS); and investment regulation in Africa.</t>
+  </si>
+  <si>
+    <t>ITT811</t>
+  </si>
+  <si>
+    <t>International Taxation Law 811</t>
+  </si>
+  <si>
+    <t>Critically analyze concepts/theories of international taxation; evaluate OECD models vs SA; interpret rules for double tax agreements; and argue for decolonized principles.</t>
+  </si>
+  <si>
+    <t>Jurisdiction (source/residence); treatment of income for different taxpayers; international headquarter companies; double tax agreements; and Constitution impact.</t>
+  </si>
+  <si>
+    <t>LAB811</t>
+  </si>
+  <si>
+    <t>Labour Law in the New Global Market 811</t>
+  </si>
+  <si>
+    <t>Collective bargaining and minimum standards in non-standard employment markets; workplace equality/affirmative action; and 4IR context.</t>
+  </si>
+  <si>
+    <t>LAB812</t>
+  </si>
+  <si>
+    <t>Law of Unfair Dismissal 812</t>
+  </si>
+  <si>
+    <t>Analyze concepts, principles, and theories relevant to dismissal development; and apply research methods and strategies.</t>
+  </si>
+  <si>
+    <t>Law of unfair dismissal.</t>
+  </si>
+  <si>
+    <t>LGG811</t>
+  </si>
+  <si>
+    <t>Constitutional Governance 811</t>
+  </si>
+  <si>
+    <t>Demonstrate understanding of rule of law principles; critically discuss SA constitutionalism; evaluate SA system in international debates; and critically analyze/solve problems.</t>
+  </si>
+  <si>
+    <t>Constitutional governance; rule of law; internal/external accountability; Chapter 9 institutions; PAIA; procurement; PAJA; review; Ubuntu; and digital impact.</t>
+  </si>
+  <si>
+    <t>LGL812</t>
+  </si>
+  <si>
+    <t>Local Government 812</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of, and ability to analyse, fundamental legal concepts, principles, theories, and practices of local government in SA.</t>
+  </si>
+  <si>
+    <t>LPS812</t>
+  </si>
+  <si>
+    <t>Punishment and Sentencing 812</t>
+  </si>
+  <si>
+    <t>Penalty clauses in international treaties; minimum/mandatory sentences; judicial discretion; mitigation/aggravation; and Bill of Rights relationship.</t>
+  </si>
+  <si>
+    <t>OML811</t>
+  </si>
+  <si>
+    <t>Int. Anti-Money Laundering Law 811</t>
+  </si>
+  <si>
+    <t>Demonstrate an understanding of how the crime of money laundering developed transnationally.</t>
+  </si>
+  <si>
+    <t>International anti-money laundering law.</t>
+  </si>
+  <si>
+    <t>PRL811</t>
+  </si>
+  <si>
+    <t>Islamic Law and Jurisprudence 811</t>
+  </si>
+  <si>
+    <t>Critically analyze schools of religious thought in Islam; assess conflict between rights approaches and scriptural interpretation; and evaluate state/non-state roles.</t>
+  </si>
+  <si>
+    <t>Muslim Personal Law.</t>
+  </si>
+  <si>
+    <t>SER811</t>
+  </si>
+  <si>
+    <t>Economic, Social and Cultural Rights 811</t>
+  </si>
+  <si>
+    <t>Understand theories relating to enforcement; apply research methods; identify international instruments/oversight bodies; and engage with separation of powers issues.</t>
+  </si>
+  <si>
+    <t>Economic, social, and cultural rights.</t>
+  </si>
+  <si>
+    <t>SIT811</t>
+  </si>
+  <si>
+    <t>Dispute Settlement in Int. Transactions 811</t>
+  </si>
+  <si>
+    <t>Demonstrate understanding of trade/investment/business transactions; evaluate conflicts; analyze settlement legitimacy based on jurisprudence; and formulate views on shortcomings.</t>
+  </si>
+  <si>
+    <t>Dispute settlement in international transactions.</t>
+  </si>
+  <si>
+    <t>TLA812</t>
+  </si>
+  <si>
+    <t>Tax Administration 812</t>
+  </si>
+  <si>
+    <t>Analyze rules under the TAA, PAJA, and the Constitution; explain taxpayer rights (privacy, property, access); and interpret rules for appeals and objections.</t>
+  </si>
+  <si>
+    <t>Provisions of TAA, PAJA, and the Constitution; inter-relationships; taxpayer rights; and court/tribunal access.</t>
+  </si>
+  <si>
+    <t>Full Thesis</t>
+  </si>
+  <si>
+    <t>Full Thesis 801 / 802</t>
+  </si>
+  <si>
+    <t>Made a satisfactory contribution to knowledge in Law or its interaction with another discipline by either proposing a significant research question or through substantial studies.</t>
+  </si>
+  <si>
+    <t>Research project in any area of Law or interaction with another field.</t>
+  </si>
+  <si>
+    <t>Mini Thesis</t>
+  </si>
+  <si>
+    <t>Mini Thesis 803 / 804</t>
+  </si>
+  <si>
+    <t>Made a limited scope contribution to knowledge in Law or interaction with another discipline following a research question with potential.</t>
+  </si>
+  <si>
+    <t>Research proposals from any area of Law; interaction with another field; and substantial historical or comparative studies.</t>
+  </si>
+  <si>
+    <t>LPF803/4</t>
+  </si>
+  <si>
+    <t>Legal Pluralism and Family Mini Thesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM 7801, LLM 7821, LLM 7822 LPFL </t>
+  </si>
+  <si>
+    <t>Made a limited scope contribution to knowledge in Law following a research question with satisfactory potential; carry out and report on research.</t>
+  </si>
+  <si>
+    <t>Mini-thesis in Legal Pluralism and Family Law.</t>
+  </si>
+  <si>
+    <t>Res. Paper</t>
+  </si>
+  <si>
+    <t>Research Paper 805 / 806</t>
+  </si>
+  <si>
+    <t>Made a limited scope contribution to knowledge in Law; carry out and report on research in an approximately 18,000-word paper suitable for publication.</t>
+  </si>
+  <si>
+    <t>Research Paper.</t>
   </si>
 </sst>
 </file>
@@ -2105,7 +3059,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2113,6 +3067,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2128,6 +3083,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2393,10 +3352,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I253"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
     <col min="6" max="6" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7446,7 +8406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" ht="349.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>383</v>
       </c>
@@ -7473,6 +8433,2268 @@
       </c>
       <c r="I175" s="1">
         <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>674</v>
+      </c>
+      <c r="B176" t="s">
+        <v>675</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176" t="s">
+        <v>676</v>
+      </c>
+      <c r="E176" t="s">
+        <v>17</v>
+      </c>
+      <c r="F176" t="s">
+        <v>17</v>
+      </c>
+      <c r="G176" t="s">
+        <v>677</v>
+      </c>
+      <c r="H176" t="s">
+        <v>678</v>
+      </c>
+      <c r="I176">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>679</v>
+      </c>
+      <c r="B177" t="s">
+        <v>680</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177" t="s">
+        <v>676</v>
+      </c>
+      <c r="E177" t="s">
+        <v>17</v>
+      </c>
+      <c r="F177" t="s">
+        <v>17</v>
+      </c>
+      <c r="G177" t="s">
+        <v>681</v>
+      </c>
+      <c r="H177" t="s">
+        <v>682</v>
+      </c>
+      <c r="I177">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>683</v>
+      </c>
+      <c r="B178" t="s">
+        <v>684</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178" t="s">
+        <v>676</v>
+      </c>
+      <c r="E178" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178" t="s">
+        <v>17</v>
+      </c>
+      <c r="G178" t="s">
+        <v>685</v>
+      </c>
+      <c r="H178" t="s">
+        <v>686</v>
+      </c>
+      <c r="I178">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>687</v>
+      </c>
+      <c r="B179" t="s">
+        <v>688</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179" t="s">
+        <v>689</v>
+      </c>
+      <c r="E179" t="s">
+        <v>17</v>
+      </c>
+      <c r="F179" t="s">
+        <v>17</v>
+      </c>
+      <c r="G179" t="s">
+        <v>690</v>
+      </c>
+      <c r="H179" t="s">
+        <v>691</v>
+      </c>
+      <c r="I179">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>692</v>
+      </c>
+      <c r="B180" t="s">
+        <v>693</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180" t="s">
+        <v>689</v>
+      </c>
+      <c r="E180" t="s">
+        <v>17</v>
+      </c>
+      <c r="F180" t="s">
+        <v>17</v>
+      </c>
+      <c r="G180" t="s">
+        <v>694</v>
+      </c>
+      <c r="H180" t="s">
+        <v>695</v>
+      </c>
+      <c r="I180">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>696</v>
+      </c>
+      <c r="B181" t="s">
+        <v>697</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181" t="s">
+        <v>689</v>
+      </c>
+      <c r="E181" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" t="s">
+        <v>17</v>
+      </c>
+      <c r="G181" t="s">
+        <v>698</v>
+      </c>
+      <c r="H181" t="s">
+        <v>699</v>
+      </c>
+      <c r="I181">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>700</v>
+      </c>
+      <c r="B182" t="s">
+        <v>701</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182" t="s">
+        <v>689</v>
+      </c>
+      <c r="E182" t="s">
+        <v>17</v>
+      </c>
+      <c r="F182" t="s">
+        <v>17</v>
+      </c>
+      <c r="G182" t="s">
+        <v>702</v>
+      </c>
+      <c r="H182" t="s">
+        <v>703</v>
+      </c>
+      <c r="I182">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>704</v>
+      </c>
+      <c r="B183" t="s">
+        <v>705</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183" t="s">
+        <v>706</v>
+      </c>
+      <c r="E183" t="s">
+        <v>17</v>
+      </c>
+      <c r="F183" t="s">
+        <v>17</v>
+      </c>
+      <c r="G183" t="s">
+        <v>707</v>
+      </c>
+      <c r="H183" t="s">
+        <v>708</v>
+      </c>
+      <c r="I183">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>709</v>
+      </c>
+      <c r="B184" t="s">
+        <v>710</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184" t="s">
+        <v>711</v>
+      </c>
+      <c r="E184" t="s">
+        <v>17</v>
+      </c>
+      <c r="F184" t="s">
+        <v>17</v>
+      </c>
+      <c r="G184" t="s">
+        <v>707</v>
+      </c>
+      <c r="H184" t="s">
+        <v>712</v>
+      </c>
+      <c r="I184">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>713</v>
+      </c>
+      <c r="B185" t="s">
+        <v>714</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185" t="s">
+        <v>711</v>
+      </c>
+      <c r="E185" t="s">
+        <v>17</v>
+      </c>
+      <c r="F185" t="s">
+        <v>17</v>
+      </c>
+      <c r="G185" t="s">
+        <v>715</v>
+      </c>
+      <c r="H185" t="s">
+        <v>716</v>
+      </c>
+      <c r="I185">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>717</v>
+      </c>
+      <c r="B186" t="s">
+        <v>718</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="s">
+        <v>711</v>
+      </c>
+      <c r="E186" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" t="s">
+        <v>17</v>
+      </c>
+      <c r="G186" t="s">
+        <v>719</v>
+      </c>
+      <c r="H186" t="s">
+        <v>720</v>
+      </c>
+      <c r="I186">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>721</v>
+      </c>
+      <c r="B187" t="s">
+        <v>722</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="s">
+        <v>676</v>
+      </c>
+      <c r="E187" t="s">
+        <v>17</v>
+      </c>
+      <c r="F187" t="s">
+        <v>17</v>
+      </c>
+      <c r="G187" t="s">
+        <v>723</v>
+      </c>
+      <c r="H187" t="s">
+        <v>724</v>
+      </c>
+      <c r="I187">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>725</v>
+      </c>
+      <c r="B188" t="s">
+        <v>726</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>676</v>
+      </c>
+      <c r="E188" t="s">
+        <v>17</v>
+      </c>
+      <c r="F188" t="s">
+        <v>17</v>
+      </c>
+      <c r="G188" t="s">
+        <v>727</v>
+      </c>
+      <c r="H188" t="s">
+        <v>728</v>
+      </c>
+      <c r="I188">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>729</v>
+      </c>
+      <c r="B189" t="s">
+        <v>730</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189" t="s">
+        <v>731</v>
+      </c>
+      <c r="E189" t="s">
+        <v>17</v>
+      </c>
+      <c r="F189" t="s">
+        <v>17</v>
+      </c>
+      <c r="G189" t="s">
+        <v>732</v>
+      </c>
+      <c r="H189" t="s">
+        <v>733</v>
+      </c>
+      <c r="I189">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>734</v>
+      </c>
+      <c r="B190" t="s">
+        <v>735</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190" t="s">
+        <v>731</v>
+      </c>
+      <c r="E190" t="s">
+        <v>17</v>
+      </c>
+      <c r="F190" t="s">
+        <v>17</v>
+      </c>
+      <c r="G190" t="s">
+        <v>736</v>
+      </c>
+      <c r="H190" t="s">
+        <v>737</v>
+      </c>
+      <c r="I190">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>738</v>
+      </c>
+      <c r="B191" t="s">
+        <v>739</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191" t="s">
+        <v>731</v>
+      </c>
+      <c r="E191" t="s">
+        <v>17</v>
+      </c>
+      <c r="F191" t="s">
+        <v>17</v>
+      </c>
+      <c r="G191" t="s">
+        <v>740</v>
+      </c>
+      <c r="H191" t="s">
+        <v>741</v>
+      </c>
+      <c r="I191">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>742</v>
+      </c>
+      <c r="B192" t="s">
+        <v>743</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="s">
+        <v>731</v>
+      </c>
+      <c r="E192" t="s">
+        <v>17</v>
+      </c>
+      <c r="F192" t="s">
+        <v>17</v>
+      </c>
+      <c r="G192" t="s">
+        <v>744</v>
+      </c>
+      <c r="H192" t="s">
+        <v>745</v>
+      </c>
+      <c r="I192">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>746</v>
+      </c>
+      <c r="B193" t="s">
+        <v>747</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193" t="s">
+        <v>676</v>
+      </c>
+      <c r="E193" t="s">
+        <v>17</v>
+      </c>
+      <c r="F193" t="s">
+        <v>17</v>
+      </c>
+      <c r="G193" t="s">
+        <v>748</v>
+      </c>
+      <c r="H193" t="s">
+        <v>749</v>
+      </c>
+      <c r="I193">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>750</v>
+      </c>
+      <c r="B194" t="s">
+        <v>751</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="s">
+        <v>752</v>
+      </c>
+      <c r="E194" t="s">
+        <v>17</v>
+      </c>
+      <c r="F194" t="s">
+        <v>17</v>
+      </c>
+      <c r="G194" t="s">
+        <v>753</v>
+      </c>
+      <c r="H194" t="s">
+        <v>754</v>
+      </c>
+      <c r="I194">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>755</v>
+      </c>
+      <c r="B195" t="s">
+        <v>756</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+      <c r="D195" t="s">
+        <v>752</v>
+      </c>
+      <c r="E195" t="s">
+        <v>17</v>
+      </c>
+      <c r="F195" t="s">
+        <v>17</v>
+      </c>
+      <c r="G195" t="s">
+        <v>757</v>
+      </c>
+      <c r="H195" t="s">
+        <v>758</v>
+      </c>
+      <c r="I195">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>759</v>
+      </c>
+      <c r="B196" t="s">
+        <v>760</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196" t="s">
+        <v>752</v>
+      </c>
+      <c r="E196" t="s">
+        <v>17</v>
+      </c>
+      <c r="F196" t="s">
+        <v>17</v>
+      </c>
+      <c r="G196" t="s">
+        <v>761</v>
+      </c>
+      <c r="H196" t="s">
+        <v>762</v>
+      </c>
+      <c r="I196">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>763</v>
+      </c>
+      <c r="B197" t="s">
+        <v>764</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="s">
+        <v>752</v>
+      </c>
+      <c r="E197" t="s">
+        <v>17</v>
+      </c>
+      <c r="F197" t="s">
+        <v>17</v>
+      </c>
+      <c r="G197" t="s">
+        <v>765</v>
+      </c>
+      <c r="H197" t="s">
+        <v>766</v>
+      </c>
+      <c r="I197">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>767</v>
+      </c>
+      <c r="B198" t="s">
+        <v>768</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198" t="s">
+        <v>769</v>
+      </c>
+      <c r="E198" t="s">
+        <v>17</v>
+      </c>
+      <c r="F198" t="s">
+        <v>17</v>
+      </c>
+      <c r="G198" t="s">
+        <v>770</v>
+      </c>
+      <c r="H198" t="s">
+        <v>771</v>
+      </c>
+      <c r="I198">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>772</v>
+      </c>
+      <c r="B199" t="s">
+        <v>773</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199" t="s">
+        <v>769</v>
+      </c>
+      <c r="E199" t="s">
+        <v>17</v>
+      </c>
+      <c r="F199" t="s">
+        <v>17</v>
+      </c>
+      <c r="G199" t="s">
+        <v>774</v>
+      </c>
+      <c r="H199" t="s">
+        <v>775</v>
+      </c>
+      <c r="I199">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>776</v>
+      </c>
+      <c r="B200" t="s">
+        <v>777</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200" t="s">
+        <v>778</v>
+      </c>
+      <c r="E200" t="s">
+        <v>17</v>
+      </c>
+      <c r="F200" t="s">
+        <v>17</v>
+      </c>
+      <c r="G200" t="s">
+        <v>779</v>
+      </c>
+      <c r="H200" t="s">
+        <v>780</v>
+      </c>
+      <c r="I200">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>781</v>
+      </c>
+      <c r="B201" t="s">
+        <v>782</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201" t="s">
+        <v>778</v>
+      </c>
+      <c r="E201" t="s">
+        <v>17</v>
+      </c>
+      <c r="F201" t="s">
+        <v>17</v>
+      </c>
+      <c r="G201" t="s">
+        <v>783</v>
+      </c>
+      <c r="H201" t="s">
+        <v>784</v>
+      </c>
+      <c r="I201">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>785</v>
+      </c>
+      <c r="B202" t="s">
+        <v>786</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+      <c r="D202" t="s">
+        <v>778</v>
+      </c>
+      <c r="E202" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" t="s">
+        <v>17</v>
+      </c>
+      <c r="G202" t="s">
+        <v>787</v>
+      </c>
+      <c r="H202" t="s">
+        <v>788</v>
+      </c>
+      <c r="I202">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>789</v>
+      </c>
+      <c r="B203" t="s">
+        <v>790</v>
+      </c>
+      <c r="C203">
+        <v>1</v>
+      </c>
+      <c r="D203" t="s">
+        <v>778</v>
+      </c>
+      <c r="E203" t="s">
+        <v>17</v>
+      </c>
+      <c r="F203" t="s">
+        <v>17</v>
+      </c>
+      <c r="G203" t="s">
+        <v>791</v>
+      </c>
+      <c r="H203" t="s">
+        <v>792</v>
+      </c>
+      <c r="I203">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>793</v>
+      </c>
+      <c r="B204" t="s">
+        <v>794</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>769</v>
+      </c>
+      <c r="E204" t="s">
+        <v>17</v>
+      </c>
+      <c r="F204" t="s">
+        <v>17</v>
+      </c>
+      <c r="G204" t="s">
+        <v>795</v>
+      </c>
+      <c r="H204" t="s">
+        <v>796</v>
+      </c>
+      <c r="I204">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>797</v>
+      </c>
+      <c r="B205" t="s">
+        <v>798</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205" t="s">
+        <v>769</v>
+      </c>
+      <c r="E205" t="s">
+        <v>17</v>
+      </c>
+      <c r="F205" t="s">
+        <v>17</v>
+      </c>
+      <c r="G205" t="s">
+        <v>799</v>
+      </c>
+      <c r="H205" t="s">
+        <v>800</v>
+      </c>
+      <c r="I205">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>801</v>
+      </c>
+      <c r="B206" t="s">
+        <v>802</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206" t="s">
+        <v>769</v>
+      </c>
+      <c r="E206" t="s">
+        <v>17</v>
+      </c>
+      <c r="F206" t="s">
+        <v>17</v>
+      </c>
+      <c r="G206" t="s">
+        <v>803</v>
+      </c>
+      <c r="H206" t="s">
+        <v>804</v>
+      </c>
+      <c r="I206">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>805</v>
+      </c>
+      <c r="B207" t="s">
+        <v>806</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207" t="s">
+        <v>778</v>
+      </c>
+      <c r="E207" t="s">
+        <v>17</v>
+      </c>
+      <c r="F207" t="s">
+        <v>17</v>
+      </c>
+      <c r="G207" t="s">
+        <v>807</v>
+      </c>
+      <c r="H207" t="s">
+        <v>808</v>
+      </c>
+      <c r="I207">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>809</v>
+      </c>
+      <c r="B208" t="s">
+        <v>810</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208" t="s">
+        <v>811</v>
+      </c>
+      <c r="E208" t="s">
+        <v>17</v>
+      </c>
+      <c r="F208" t="s">
+        <v>17</v>
+      </c>
+      <c r="G208" t="s">
+        <v>812</v>
+      </c>
+      <c r="H208" t="s">
+        <v>813</v>
+      </c>
+      <c r="I208">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>814</v>
+      </c>
+      <c r="B209" t="s">
+        <v>815</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209" t="s">
+        <v>811</v>
+      </c>
+      <c r="E209" t="s">
+        <v>17</v>
+      </c>
+      <c r="F209" t="s">
+        <v>17</v>
+      </c>
+      <c r="G209" t="s">
+        <v>748</v>
+      </c>
+      <c r="H209" t="s">
+        <v>816</v>
+      </c>
+      <c r="I209">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>817</v>
+      </c>
+      <c r="B210" t="s">
+        <v>818</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210" t="s">
+        <v>778</v>
+      </c>
+      <c r="E210" t="s">
+        <v>819</v>
+      </c>
+      <c r="F210" t="s">
+        <v>17</v>
+      </c>
+      <c r="G210" t="s">
+        <v>820</v>
+      </c>
+      <c r="H210" t="s">
+        <v>821</v>
+      </c>
+      <c r="I210">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>822</v>
+      </c>
+      <c r="B211" t="s">
+        <v>823</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="D211" t="s">
+        <v>778</v>
+      </c>
+      <c r="E211" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" t="s">
+        <v>17</v>
+      </c>
+      <c r="G211" t="s">
+        <v>824</v>
+      </c>
+      <c r="H211" t="s">
+        <v>825</v>
+      </c>
+      <c r="I211">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>826</v>
+      </c>
+      <c r="B212" t="s">
+        <v>827</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212" t="s">
+        <v>769</v>
+      </c>
+      <c r="E212" t="s">
+        <v>822</v>
+      </c>
+      <c r="F212" t="s">
+        <v>17</v>
+      </c>
+      <c r="G212" t="s">
+        <v>828</v>
+      </c>
+      <c r="H212" t="s">
+        <v>829</v>
+      </c>
+      <c r="I212">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>830</v>
+      </c>
+      <c r="B213" t="s">
+        <v>831</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213" t="s">
+        <v>778</v>
+      </c>
+      <c r="E213" t="s">
+        <v>17</v>
+      </c>
+      <c r="F213" t="s">
+        <v>17</v>
+      </c>
+      <c r="G213" t="s">
+        <v>832</v>
+      </c>
+      <c r="H213" t="s">
+        <v>833</v>
+      </c>
+      <c r="I213">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>834</v>
+      </c>
+      <c r="B214" t="s">
+        <v>835</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="D214" t="s">
+        <v>778</v>
+      </c>
+      <c r="E214" t="s">
+        <v>17</v>
+      </c>
+      <c r="F214" t="s">
+        <v>17</v>
+      </c>
+      <c r="G214" t="s">
+        <v>836</v>
+      </c>
+      <c r="H214" t="s">
+        <v>837</v>
+      </c>
+      <c r="I214">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>838</v>
+      </c>
+      <c r="B215" t="s">
+        <v>839</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215" t="s">
+        <v>778</v>
+      </c>
+      <c r="E215" t="s">
+        <v>17</v>
+      </c>
+      <c r="F215" t="s">
+        <v>17</v>
+      </c>
+      <c r="G215" t="s">
+        <v>840</v>
+      </c>
+      <c r="H215" t="s">
+        <v>841</v>
+      </c>
+      <c r="I215">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>842</v>
+      </c>
+      <c r="B216" t="s">
+        <v>843</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216" t="s">
+        <v>769</v>
+      </c>
+      <c r="E216" t="s">
+        <v>17</v>
+      </c>
+      <c r="F216" t="s">
+        <v>17</v>
+      </c>
+      <c r="G216" t="s">
+        <v>844</v>
+      </c>
+      <c r="H216" t="s">
+        <v>845</v>
+      </c>
+      <c r="I216">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>846</v>
+      </c>
+      <c r="B217" t="s">
+        <v>847</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+      <c r="D217" t="s">
+        <v>769</v>
+      </c>
+      <c r="E217" t="s">
+        <v>17</v>
+      </c>
+      <c r="F217" t="s">
+        <v>17</v>
+      </c>
+      <c r="G217" t="s">
+        <v>848</v>
+      </c>
+      <c r="H217" t="s">
+        <v>849</v>
+      </c>
+      <c r="I217">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>850</v>
+      </c>
+      <c r="B218" t="s">
+        <v>851</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218" t="s">
+        <v>778</v>
+      </c>
+      <c r="E218" t="s">
+        <v>17</v>
+      </c>
+      <c r="F218" t="s">
+        <v>17</v>
+      </c>
+      <c r="G218" t="s">
+        <v>852</v>
+      </c>
+      <c r="H218" t="s">
+        <v>853</v>
+      </c>
+      <c r="I218">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>854</v>
+      </c>
+      <c r="B219" t="s">
+        <v>855</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219" t="s">
+        <v>778</v>
+      </c>
+      <c r="E219" t="s">
+        <v>17</v>
+      </c>
+      <c r="F219" t="s">
+        <v>17</v>
+      </c>
+      <c r="G219" t="s">
+        <v>856</v>
+      </c>
+      <c r="H219" t="s">
+        <v>857</v>
+      </c>
+      <c r="I219">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>858</v>
+      </c>
+      <c r="B220" t="s">
+        <v>859</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220" t="s">
+        <v>778</v>
+      </c>
+      <c r="E220" t="s">
+        <v>17</v>
+      </c>
+      <c r="F220" t="s">
+        <v>17</v>
+      </c>
+      <c r="G220" t="s">
+        <v>860</v>
+      </c>
+      <c r="H220" t="s">
+        <v>861</v>
+      </c>
+      <c r="I220">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>862</v>
+      </c>
+      <c r="B221" t="s">
+        <v>863</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221" t="s">
+        <v>778</v>
+      </c>
+      <c r="E221" t="s">
+        <v>17</v>
+      </c>
+      <c r="F221" t="s">
+        <v>17</v>
+      </c>
+      <c r="G221" t="s">
+        <v>864</v>
+      </c>
+      <c r="H221" t="s">
+        <v>865</v>
+      </c>
+      <c r="I221">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>866</v>
+      </c>
+      <c r="B222" t="s">
+        <v>867</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222" t="s">
+        <v>778</v>
+      </c>
+      <c r="E222" t="s">
+        <v>17</v>
+      </c>
+      <c r="F222" t="s">
+        <v>17</v>
+      </c>
+      <c r="G222" t="s">
+        <v>868</v>
+      </c>
+      <c r="H222" t="s">
+        <v>869</v>
+      </c>
+      <c r="I222">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>870</v>
+      </c>
+      <c r="B223" t="s">
+        <v>871</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="s">
+        <v>778</v>
+      </c>
+      <c r="E223" t="s">
+        <v>17</v>
+      </c>
+      <c r="F223" t="s">
+        <v>17</v>
+      </c>
+      <c r="G223" t="s">
+        <v>740</v>
+      </c>
+      <c r="H223" t="s">
+        <v>872</v>
+      </c>
+      <c r="I223">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>873</v>
+      </c>
+      <c r="B224" t="s">
+        <v>874</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224" t="s">
+        <v>778</v>
+      </c>
+      <c r="E224" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224" t="s">
+        <v>17</v>
+      </c>
+      <c r="G224" t="s">
+        <v>875</v>
+      </c>
+      <c r="H224" t="s">
+        <v>876</v>
+      </c>
+      <c r="I224">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>877</v>
+      </c>
+      <c r="B225" t="s">
+        <v>878</v>
+      </c>
+      <c r="C225">
+        <v>1</v>
+      </c>
+      <c r="D225" t="s">
+        <v>811</v>
+      </c>
+      <c r="E225" t="s">
+        <v>17</v>
+      </c>
+      <c r="F225" t="s">
+        <v>814</v>
+      </c>
+      <c r="G225" t="s">
+        <v>879</v>
+      </c>
+      <c r="H225" t="s">
+        <v>880</v>
+      </c>
+      <c r="I225">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>881</v>
+      </c>
+      <c r="B226" t="s">
+        <v>882</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
+        <v>778</v>
+      </c>
+      <c r="E226" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226" t="s">
+        <v>17</v>
+      </c>
+      <c r="G226" t="s">
+        <v>883</v>
+      </c>
+      <c r="H226" t="s">
+        <v>884</v>
+      </c>
+      <c r="I226">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>885</v>
+      </c>
+      <c r="B227" t="s">
+        <v>886</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+      <c r="D227" t="s">
+        <v>778</v>
+      </c>
+      <c r="E227" t="s">
+        <v>17</v>
+      </c>
+      <c r="F227" t="s">
+        <v>887</v>
+      </c>
+      <c r="G227" t="s">
+        <v>888</v>
+      </c>
+      <c r="H227" t="s">
+        <v>889</v>
+      </c>
+      <c r="I227">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>819</v>
+      </c>
+      <c r="B228" t="s">
+        <v>890</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228" t="s">
+        <v>778</v>
+      </c>
+      <c r="E228" t="s">
+        <v>17</v>
+      </c>
+      <c r="F228" t="s">
+        <v>891</v>
+      </c>
+      <c r="G228" t="s">
+        <v>892</v>
+      </c>
+      <c r="H228" t="s">
+        <v>893</v>
+      </c>
+      <c r="I228">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>894</v>
+      </c>
+      <c r="B229" t="s">
+        <v>895</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229" t="s">
+        <v>778</v>
+      </c>
+      <c r="E229" t="s">
+        <v>17</v>
+      </c>
+      <c r="F229" t="s">
+        <v>17</v>
+      </c>
+      <c r="G229" t="s">
+        <v>896</v>
+      </c>
+      <c r="H229" t="s">
+        <v>897</v>
+      </c>
+      <c r="I229">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>898</v>
+      </c>
+      <c r="B230" t="s">
+        <v>899</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="D230" t="s">
+        <v>778</v>
+      </c>
+      <c r="E230" t="s">
+        <v>17</v>
+      </c>
+      <c r="F230" t="s">
+        <v>17</v>
+      </c>
+      <c r="G230" t="s">
+        <v>900</v>
+      </c>
+      <c r="H230" t="s">
+        <v>901</v>
+      </c>
+      <c r="I230">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>902</v>
+      </c>
+      <c r="B231" t="s">
+        <v>903</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231" t="s">
+        <v>778</v>
+      </c>
+      <c r="E231" t="s">
+        <v>17</v>
+      </c>
+      <c r="F231" t="s">
+        <v>17</v>
+      </c>
+      <c r="G231" t="s">
+        <v>740</v>
+      </c>
+      <c r="H231" t="s">
+        <v>904</v>
+      </c>
+      <c r="I231">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>905</v>
+      </c>
+      <c r="B232" t="s">
+        <v>906</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232" t="s">
+        <v>811</v>
+      </c>
+      <c r="E232" t="s">
+        <v>17</v>
+      </c>
+      <c r="F232" t="s">
+        <v>17</v>
+      </c>
+      <c r="G232" t="s">
+        <v>907</v>
+      </c>
+      <c r="H232" t="s">
+        <v>908</v>
+      </c>
+      <c r="I232">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>909</v>
+      </c>
+      <c r="B233" t="s">
+        <v>910</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233" t="s">
+        <v>778</v>
+      </c>
+      <c r="E233" t="s">
+        <v>17</v>
+      </c>
+      <c r="F233" t="s">
+        <v>17</v>
+      </c>
+      <c r="G233" t="s">
+        <v>911</v>
+      </c>
+      <c r="H233" t="s">
+        <v>912</v>
+      </c>
+      <c r="I233">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>913</v>
+      </c>
+      <c r="B234" t="s">
+        <v>914</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234" t="s">
+        <v>778</v>
+      </c>
+      <c r="E234" t="s">
+        <v>17</v>
+      </c>
+      <c r="F234" t="s">
+        <v>17</v>
+      </c>
+      <c r="G234" t="s">
+        <v>915</v>
+      </c>
+      <c r="H234" t="s">
+        <v>916</v>
+      </c>
+      <c r="I234">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>917</v>
+      </c>
+      <c r="B235" t="s">
+        <v>918</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235" t="s">
+        <v>778</v>
+      </c>
+      <c r="E235" t="s">
+        <v>17</v>
+      </c>
+      <c r="F235" t="s">
+        <v>17</v>
+      </c>
+      <c r="G235" t="s">
+        <v>919</v>
+      </c>
+      <c r="H235" t="s">
+        <v>920</v>
+      </c>
+      <c r="I235">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>921</v>
+      </c>
+      <c r="B236" t="s">
+        <v>922</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236" t="s">
+        <v>778</v>
+      </c>
+      <c r="E236" t="s">
+        <v>17</v>
+      </c>
+      <c r="F236" t="s">
+        <v>17</v>
+      </c>
+      <c r="G236" t="s">
+        <v>923</v>
+      </c>
+      <c r="H236" t="s">
+        <v>924</v>
+      </c>
+      <c r="I236">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>925</v>
+      </c>
+      <c r="B237" t="s">
+        <v>926</v>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+      <c r="D237" t="s">
+        <v>927</v>
+      </c>
+      <c r="E237" t="s">
+        <v>17</v>
+      </c>
+      <c r="F237" t="s">
+        <v>17</v>
+      </c>
+      <c r="G237" t="s">
+        <v>928</v>
+      </c>
+      <c r="H237" t="s">
+        <v>929</v>
+      </c>
+      <c r="I237">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>930</v>
+      </c>
+      <c r="B238" t="s">
+        <v>931</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+      <c r="D238" t="s">
+        <v>927</v>
+      </c>
+      <c r="E238" t="s">
+        <v>17</v>
+      </c>
+      <c r="F238" t="s">
+        <v>17</v>
+      </c>
+      <c r="G238" t="s">
+        <v>932</v>
+      </c>
+      <c r="H238" t="s">
+        <v>933</v>
+      </c>
+      <c r="I238">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>934</v>
+      </c>
+      <c r="B239" t="s">
+        <v>935</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+      <c r="D239" t="s">
+        <v>778</v>
+      </c>
+      <c r="E239" t="s">
+        <v>17</v>
+      </c>
+      <c r="F239" t="s">
+        <v>17</v>
+      </c>
+      <c r="G239" t="s">
+        <v>936</v>
+      </c>
+      <c r="H239" t="s">
+        <v>937</v>
+      </c>
+      <c r="I239">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>938</v>
+      </c>
+      <c r="B240" t="s">
+        <v>939</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+      <c r="D240" t="s">
+        <v>778</v>
+      </c>
+      <c r="E240" t="s">
+        <v>17</v>
+      </c>
+      <c r="F240" t="s">
+        <v>17</v>
+      </c>
+      <c r="G240" t="s">
+        <v>740</v>
+      </c>
+      <c r="H240" t="s">
+        <v>940</v>
+      </c>
+      <c r="I240">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>941</v>
+      </c>
+      <c r="B241" t="s">
+        <v>942</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+      <c r="D241" t="s">
+        <v>778</v>
+      </c>
+      <c r="E241" t="s">
+        <v>17</v>
+      </c>
+      <c r="F241" t="s">
+        <v>17</v>
+      </c>
+      <c r="G241" t="s">
+        <v>943</v>
+      </c>
+      <c r="H241" t="s">
+        <v>944</v>
+      </c>
+      <c r="I241">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>945</v>
+      </c>
+      <c r="B242" t="s">
+        <v>946</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242" t="s">
+        <v>778</v>
+      </c>
+      <c r="E242" t="s">
+        <v>17</v>
+      </c>
+      <c r="F242" t="s">
+        <v>17</v>
+      </c>
+      <c r="G242" t="s">
+        <v>947</v>
+      </c>
+      <c r="H242" t="s">
+        <v>948</v>
+      </c>
+      <c r="I242">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>949</v>
+      </c>
+      <c r="B243" t="s">
+        <v>950</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+      <c r="D243" t="s">
+        <v>778</v>
+      </c>
+      <c r="E243" t="s">
+        <v>17</v>
+      </c>
+      <c r="F243" t="s">
+        <v>17</v>
+      </c>
+      <c r="G243" t="s">
+        <v>951</v>
+      </c>
+      <c r="H243" t="s">
+        <v>728</v>
+      </c>
+      <c r="I243">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>952</v>
+      </c>
+      <c r="B244" t="s">
+        <v>953</v>
+      </c>
+      <c r="C244">
+        <v>1</v>
+      </c>
+      <c r="D244" t="s">
+        <v>769</v>
+      </c>
+      <c r="E244" t="s">
+        <v>17</v>
+      </c>
+      <c r="F244" t="s">
+        <v>17</v>
+      </c>
+      <c r="G244" t="s">
+        <v>774</v>
+      </c>
+      <c r="H244" t="s">
+        <v>954</v>
+      </c>
+      <c r="I244">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>955</v>
+      </c>
+      <c r="B245" t="s">
+        <v>956</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="D245" t="s">
+        <v>778</v>
+      </c>
+      <c r="E245" t="s">
+        <v>17</v>
+      </c>
+      <c r="F245" t="s">
+        <v>17</v>
+      </c>
+      <c r="G245" t="s">
+        <v>957</v>
+      </c>
+      <c r="H245" t="s">
+        <v>958</v>
+      </c>
+      <c r="I245">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>959</v>
+      </c>
+      <c r="B246" t="s">
+        <v>960</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+      <c r="D246" t="s">
+        <v>811</v>
+      </c>
+      <c r="E246" t="s">
+        <v>17</v>
+      </c>
+      <c r="F246" t="s">
+        <v>17</v>
+      </c>
+      <c r="G246" t="s">
+        <v>961</v>
+      </c>
+      <c r="H246" t="s">
+        <v>962</v>
+      </c>
+      <c r="I246">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>963</v>
+      </c>
+      <c r="B247" t="s">
+        <v>964</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="D247" t="s">
+        <v>778</v>
+      </c>
+      <c r="E247" t="s">
+        <v>17</v>
+      </c>
+      <c r="F247" t="s">
+        <v>17</v>
+      </c>
+      <c r="G247" t="s">
+        <v>965</v>
+      </c>
+      <c r="H247" t="s">
+        <v>966</v>
+      </c>
+      <c r="I247">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>967</v>
+      </c>
+      <c r="B248" t="s">
+        <v>968</v>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+      <c r="D248" t="s">
+        <v>778</v>
+      </c>
+      <c r="E248" t="s">
+        <v>17</v>
+      </c>
+      <c r="F248" t="s">
+        <v>17</v>
+      </c>
+      <c r="G248" t="s">
+        <v>969</v>
+      </c>
+      <c r="H248" t="s">
+        <v>970</v>
+      </c>
+      <c r="I248">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>971</v>
+      </c>
+      <c r="B249" t="s">
+        <v>972</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+      <c r="D249" t="s">
+        <v>769</v>
+      </c>
+      <c r="E249" t="s">
+        <v>17</v>
+      </c>
+      <c r="F249" t="s">
+        <v>17</v>
+      </c>
+      <c r="G249" t="s">
+        <v>973</v>
+      </c>
+      <c r="H249" t="s">
+        <v>974</v>
+      </c>
+      <c r="I249">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>975</v>
+      </c>
+      <c r="B250" t="s">
+        <v>976</v>
+      </c>
+      <c r="C250" s="3">
+        <v>46024</v>
+      </c>
+      <c r="D250" t="s">
+        <v>811</v>
+      </c>
+      <c r="E250" t="s">
+        <v>17</v>
+      </c>
+      <c r="F250" t="s">
+        <v>17</v>
+      </c>
+      <c r="G250" t="s">
+        <v>977</v>
+      </c>
+      <c r="H250" t="s">
+        <v>978</v>
+      </c>
+      <c r="I250">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>979</v>
+      </c>
+      <c r="B251" t="s">
+        <v>980</v>
+      </c>
+      <c r="C251" s="3">
+        <v>46024</v>
+      </c>
+      <c r="D251" t="s">
+        <v>811</v>
+      </c>
+      <c r="E251" t="s">
+        <v>17</v>
+      </c>
+      <c r="F251" t="s">
+        <v>17</v>
+      </c>
+      <c r="G251" t="s">
+        <v>981</v>
+      </c>
+      <c r="H251" t="s">
+        <v>982</v>
+      </c>
+      <c r="I251">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>983</v>
+      </c>
+      <c r="B252" t="s">
+        <v>984</v>
+      </c>
+      <c r="C252" s="3">
+        <v>46024</v>
+      </c>
+      <c r="D252" t="s">
+        <v>985</v>
+      </c>
+      <c r="E252" t="s">
+        <v>17</v>
+      </c>
+      <c r="F252" t="s">
+        <v>17</v>
+      </c>
+      <c r="G252" t="s">
+        <v>986</v>
+      </c>
+      <c r="H252" t="s">
+        <v>987</v>
+      </c>
+      <c r="I252">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>988</v>
+      </c>
+      <c r="B253" t="s">
+        <v>989</v>
+      </c>
+      <c r="C253" s="3">
+        <v>46024</v>
+      </c>
+      <c r="D253" t="s">
+        <v>778</v>
+      </c>
+      <c r="E253" t="s">
+        <v>17</v>
+      </c>
+      <c r="F253" t="s">
+        <v>17</v>
+      </c>
+      <c r="G253" t="s">
+        <v>990</v>
+      </c>
+      <c r="H253" t="s">
+        <v>991</v>
+      </c>
+      <c r="I253">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
